--- a/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2_Test.xlsx
+++ b/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2_Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\share\OneDrive\Documents\Personal Projects\GOGO Kart\CAD\GOGO_KART_FSAE\Suspension\3D_Suspension_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D2A1CE-7CE1-439A-84B4-18A44494CA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D8389F6-7F5B-4CE0-86E2-1C4545728BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4152" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suspension Analyzer" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Hand Calcs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -897,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -945,34 +946,33 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,6 +1013,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.37345077160493828"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1344,12 +1352,20 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="800"/>
                   <a:t>Wheel travel (mm)   [+bump / -droop]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.3238168209876543"/>
+              <c:y val="0.95829338741711334"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="0.000" sourceLinked="1"/>
@@ -1434,6 +1450,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.34857500000000002"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1930,12 +1954,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>604631</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6480000" cy="3240000"/>
+    <xdr:ext cx="7101195" cy="3901108"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 1">
@@ -1961,12 +1985,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>612913</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6480000" cy="3240000"/>
+    <xdr:ext cx="6480000" cy="3768587"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 2">
@@ -2311,22 +2335,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C2:BI67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="159" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="153.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="153.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" customWidth="1"/>
+    <col min="13" max="13" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="9" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" customWidth="1"/>
     <col min="23" max="25" width="9" bestFit="1" customWidth="1"/>
@@ -2335,120 +2359,80 @@
     <col min="31" max="61" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:61" x14ac:dyDescent="0.25">
-      <c r="T2" s="26" t="s">
+    <row r="2" spans="3:61" x14ac:dyDescent="0.3">
+      <c r="T2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="28">
+      <c r="W2" s="20">
         <v>0</v>
       </c>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
     </row>
-    <row r="3" spans="3:61" x14ac:dyDescent="0.25">
-      <c r="C3" s="25" t="s">
+    <row r="3" spans="3:61" x14ac:dyDescent="0.3">
+      <c r="C3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
-      <c r="H3" s="25" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="H3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
-      <c r="M3" s="19" t="s">
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
+      <c r="M3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="21"/>
-      <c r="T3" s="32" t="s">
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="29"/>
+      <c r="T3" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
-      <c r="AG3" s="33"/>
-      <c r="AH3" s="33"/>
-      <c r="AI3" s="33"/>
-      <c r="AJ3" s="33"/>
-      <c r="AK3" s="33"/>
-      <c r="AL3" s="33"/>
-      <c r="AM3" s="33"/>
-      <c r="AN3" s="33"/>
-      <c r="AO3" s="33"/>
-      <c r="AP3" s="33"/>
-      <c r="AQ3" s="33"/>
-      <c r="AR3" s="33"/>
-      <c r="AS3" s="33"/>
-      <c r="AT3" s="33"/>
-      <c r="AU3" s="33"/>
-      <c r="AV3" s="33"/>
-      <c r="AW3" s="33"/>
-      <c r="AX3" s="33"/>
-      <c r="AY3" s="33"/>
-      <c r="AZ3" s="33"/>
-      <c r="BA3" s="33"/>
-      <c r="BB3" s="33"/>
-      <c r="BC3" s="33"/>
-      <c r="BD3" s="33"/>
-      <c r="BE3" s="33"/>
-      <c r="BF3" s="33"/>
-      <c r="BG3" s="33"/>
-      <c r="BH3" s="33"/>
-      <c r="BI3" s="33"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
+      <c r="BI3" s="31"/>
     </row>
-    <row r="4" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2488,134 +2472,134 @@
       <c r="Q4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="T4" s="29" t="s">
+      <c r="T4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="U4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="V4" s="29" t="s">
+      <c r="V4" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="29" t="s">
+      <c r="X4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="Y4" s="29" t="s">
+      <c r="Y4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="Z4" s="29" t="s">
+      <c r="Z4" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AA4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="29" t="s">
+      <c r="AB4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="AC4" s="29" t="s">
+      <c r="AC4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="AD4" s="29" t="s">
+      <c r="AD4" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AE4" s="29" t="s">
+      <c r="AE4" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AF4" s="29" t="s">
+      <c r="AF4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AG4" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="AH4" s="29" t="s">
+      <c r="AH4" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AI4" s="29" t="s">
+      <c r="AI4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AJ4" s="29" t="s">
+      <c r="AJ4" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="AK4" s="29" t="s">
+      <c r="AK4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AL4" s="29" t="s">
+      <c r="AL4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AM4" s="29" t="s">
+      <c r="AM4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AN4" s="29" t="s">
+      <c r="AN4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="AO4" s="29" t="s">
+      <c r="AO4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="AP4" s="29" t="s">
+      <c r="AP4" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="AQ4" s="29" t="s">
+      <c r="AQ4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AR4" s="29" t="s">
+      <c r="AR4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="AS4" s="29" t="s">
+      <c r="AS4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="AT4" s="29" t="s">
+      <c r="AT4" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AU4" s="29" t="s">
+      <c r="AU4" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="AV4" s="29" t="s">
+      <c r="AV4" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AW4" s="29" t="s">
+      <c r="AW4" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="AX4" s="29" t="s">
+      <c r="AX4" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AY4" s="29" t="s">
+      <c r="AY4" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="AZ4" s="29" t="s">
+      <c r="AZ4" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="BA4" s="29" t="s">
+      <c r="BA4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="BB4" s="29" t="s">
+      <c r="BB4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="BC4" s="29" t="s">
+      <c r="BC4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="BD4" s="29" t="s">
+      <c r="BD4" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="BE4" s="29" t="s">
+      <c r="BE4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="BF4" s="29" t="s">
+      <c r="BF4" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="BG4" s="29" t="s">
+      <c r="BG4" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="BH4" s="29" t="s">
+      <c r="BH4" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="BI4" s="29" t="s">
+      <c r="BI4" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>55</v>
       </c>
@@ -2653,175 +2637,175 @@
       <c r="Q5" s="14">
         <v>400</v>
       </c>
-      <c r="T5" s="30">
+      <c r="T5" s="22">
         <v>-20</v>
       </c>
-      <c r="U5" s="31" t="e">
+      <c r="U5" s="23" t="e">
         <f t="shared" ref="U5:U45" si="0">$D$5+$D$22*COS(RADIANS(T5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="V5" s="31" t="e">
+      <c r="V5" s="23" t="e">
         <f t="shared" ref="V5:V45" si="1">$D$6+$D$22*SIN(RADIANS(T5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="W5" s="31" t="e">
+      <c r="W5" s="23" t="e">
         <f t="shared" ref="W5:W45" si="2">SQRT((U5-$D$7)^2+(V5-$D$8)^2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="X5" s="31" t="e">
+      <c r="X5" s="23" t="e">
         <f t="shared" ref="X5:X45" si="3">DEGREES(ATAN((V5-$D$8)/(U5-$D$7)))</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y5" s="31" t="e">
+      <c r="Y5" s="23" t="e">
         <f t="shared" ref="Y5:Y45" si="4">DEGREES(ACOS(($D$23^2+W5^2-$D$27^2)/(2*$D$23*W5)))</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z5" s="31" t="e">
+      <c r="Z5" s="23" t="e">
         <f t="shared" ref="Z5:Z45" si="5">X5+$D$33*Y5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA5" s="31" t="e">
+      <c r="AA5" s="23" t="e">
         <f t="shared" ref="AA5:AA45" si="6">$D$7+$D$23*COS(RADIANS(Z5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="AB5" s="31" t="e">
+      <c r="AB5" s="23" t="e">
         <f t="shared" ref="AB5:AB45" si="7">$D$8+$D$23*SIN(RADIANS(Z5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="AC5" s="31" t="e">
+      <c r="AC5" s="23" t="e">
         <f t="shared" ref="AC5:AC45" si="8">-DEGREES(ATAN((U5-AA5)/(V5-AB5)))</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD5" s="31" t="e">
+      <c r="AD5" s="23" t="e">
         <f t="shared" ref="AD5:AD45" si="9">AC5+$W$2</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE5" s="31" t="e">
+      <c r="AE5" s="23" t="e">
         <f t="shared" ref="AE5:AE45" si="10">$D$26/$D$11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF5" s="31" t="e">
+      <c r="AF5" s="23" t="e">
         <f t="shared" ref="AF5:AF45" si="11">(U5-AA5)/$D$11</f>
         <v>#NUM!</v>
       </c>
-      <c r="AG5" s="31" t="e">
+      <c r="AG5" s="23" t="e">
         <f t="shared" ref="AG5:AG45" si="12">(V5-AB5)/$D$11</f>
         <v>#NUM!</v>
       </c>
-      <c r="AH5" s="31" t="e">
+      <c r="AH5" s="23" t="e">
         <f t="shared" ref="AH5:AH45" si="13">AC5-$I$36</f>
         <v>#NUM!</v>
       </c>
-      <c r="AI5" s="31">
+      <c r="AI5" s="23">
         <f t="shared" ref="AI5:AI45" si="14">$I$8</f>
         <v>0</v>
       </c>
-      <c r="AJ5" s="31" t="e">
+      <c r="AJ5" s="23" t="e">
         <f t="shared" ref="AJ5:AJ45" si="15">$I$9*COS(RADIANS(AH5))-$I$10*SIN(RADIANS(AH5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK5" s="31" t="e">
+      <c r="AK5" s="23" t="e">
         <f t="shared" ref="AK5:AK45" si="16">$I$9*SIN(RADIANS(AH5))+$I$10*COS(RADIANS(AH5))</f>
         <v>#NUM!</v>
       </c>
-      <c r="AL5" s="31" t="e">
+      <c r="AL5" s="23" t="e">
         <f t="shared" ref="AL5:AL45" si="17">AI5*AE5+AJ5*AF5+AK5*AG5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM5" s="31" t="e">
+      <c r="AM5" s="23" t="e">
         <f t="shared" ref="AM5:AM45" si="18">AI5-AL5*AE5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN5" s="31" t="e">
+      <c r="AN5" s="23" t="e">
         <f t="shared" ref="AN5:AN45" si="19">AJ5-AL5*AF5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AO5" s="31" t="e">
+      <c r="AO5" s="23" t="e">
         <f t="shared" ref="AO5:AO45" si="20">AK5-AL5*AG5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AP5" s="31" t="e">
+      <c r="AP5" s="23" t="e">
         <f t="shared" ref="AP5:AP45" si="21">SQRT(AM5^2+AN5^2+AO5^2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ5" s="31" t="e">
+      <c r="AQ5" s="23" t="e">
         <f t="shared" ref="AQ5:AQ45" si="22">AF5*AK5-AG5*AJ5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AR5" s="31" t="e">
+      <c r="AR5" s="23" t="e">
         <f t="shared" ref="AR5:AR45" si="23">AG5*AI5-AE5*AK5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AS5" s="31" t="e">
+      <c r="AS5" s="23" t="e">
         <f t="shared" ref="AS5:AS45" si="24">AE5*AJ5-AF5*AI5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT5" s="31" t="e">
+      <c r="AT5" s="23" t="e">
         <f t="shared" ref="AT5:AT45" si="25">$D$25+AL5*AE5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU5" s="31" t="e">
+      <c r="AU5" s="23" t="e">
         <f t="shared" ref="AU5:AU45" si="26">AA5+AL5*AF5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AV5" s="31" t="e">
+      <c r="AV5" s="23" t="e">
         <f t="shared" ref="AV5:AV45" si="27">AB5+AL5*AG5</f>
         <v>#NUM!</v>
       </c>
-      <c r="AW5" s="31" t="e">
+      <c r="AW5" s="23" t="e">
         <f t="shared" ref="AW5:AW45" si="28">AT5-$I$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX5" s="31" t="e">
+      <c r="AX5" s="23" t="e">
         <f t="shared" ref="AX5:AX45" si="29">AU5-$I$6</f>
         <v>#NUM!</v>
       </c>
-      <c r="AY5" s="31" t="e">
+      <c r="AY5" s="23" t="e">
         <f t="shared" ref="AY5:AY45" si="30">AV5-$I$7</f>
         <v>#NUM!</v>
       </c>
-      <c r="AZ5" s="30" t="e">
+      <c r="AZ5" s="22" t="e">
         <f t="shared" ref="AZ5:AZ45" si="31">2*(AW5*AM5+AX5*AN5+AY5*AO5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA5" s="30" t="e">
+      <c r="BA5" s="22" t="e">
         <f t="shared" ref="BA5:BA45" si="32">2*(AW5*AQ5+AX5*AR5+AY5*AS5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB5" s="30" t="e">
+      <c r="BB5" s="22" t="e">
         <f t="shared" ref="BB5:BB45" si="33">$I$31^2-(AW5^2+AX5^2+AY5^2)-AP5^2</f>
         <v>#NUM!</v>
       </c>
-      <c r="BC5" s="30" t="e">
+      <c r="BC5" s="22" t="e">
         <f t="shared" ref="BC5:BC45" si="34">SQRT(AZ5^2+BA5^2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD5" s="31" t="e">
+      <c r="BD5" s="23" t="e">
         <f t="shared" ref="BD5:BD45" si="35">DEGREES(ATAN2(AZ5,BA5))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE5" s="31" t="e">
+      <c r="BE5" s="23" t="e">
         <f t="shared" ref="BE5:BE45" si="36">IFERROR(BD5+$I$12*DEGREES(ACOS(BB5/BC5)),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="BF5" s="31" t="e">
+      <c r="BF5" s="23" t="e">
         <f t="shared" ref="BF5:BF45" si="37">IFERROR(COS(RADIANS(BE5))+AE5^2*(1-COS(RADIANS(BE5))),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="BG5" s="31" t="e">
+      <c r="BG5" s="23" t="e">
         <f t="shared" ref="BG5:BG45" si="38">IFERROR(AG5*SIN(RADIANS(BE5))+AE5*AF5*(1-COS(RADIANS(BE5))),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="BH5" s="31" t="e">
+      <c r="BH5" s="23" t="e">
         <f t="shared" ref="BH5:BH45" si="39">IFERROR($I$11+DEGREES(ATAN2(BF5,BG5)),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="BI5" s="31" t="e">
+      <c r="BI5" s="23" t="e">
         <f t="shared" ref="BI5:BI45" si="40">AB5-$I$24</f>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="6" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
         <v>61</v>
       </c>
@@ -2859,175 +2843,175 @@
       <c r="Q6" s="16">
         <v>274</v>
       </c>
-      <c r="T6" s="30">
+      <c r="T6" s="22">
         <v>-19</v>
       </c>
-      <c r="U6" s="31" t="e">
+      <c r="U6" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V6" s="31" t="e">
+      <c r="V6" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W6" s="31" t="e">
+      <c r="W6" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X6" s="31" t="e">
+      <c r="X6" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y6" s="31" t="e">
+      <c r="Y6" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z6" s="31" t="e">
+      <c r="Z6" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA6" s="31" t="e">
+      <c r="AA6" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB6" s="31" t="e">
+      <c r="AB6" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC6" s="31" t="e">
+      <c r="AC6" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD6" s="31" t="e">
+      <c r="AD6" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE6" s="31" t="e">
+      <c r="AE6" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF6" s="31" t="e">
+      <c r="AF6" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG6" s="31" t="e">
+      <c r="AG6" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH6" s="31" t="e">
+      <c r="AH6" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI6" s="31">
+      <c r="AI6" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ6" s="31" t="e">
+      <c r="AJ6" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK6" s="31" t="e">
+      <c r="AK6" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL6" s="31" t="e">
+      <c r="AL6" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM6" s="31" t="e">
+      <c r="AM6" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN6" s="31" t="e">
+      <c r="AN6" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO6" s="31" t="e">
+      <c r="AO6" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP6" s="31" t="e">
+      <c r="AP6" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ6" s="31" t="e">
+      <c r="AQ6" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR6" s="31" t="e">
+      <c r="AR6" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS6" s="31" t="e">
+      <c r="AS6" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT6" s="31" t="e">
+      <c r="AT6" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU6" s="31" t="e">
+      <c r="AU6" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV6" s="31" t="e">
+      <c r="AV6" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW6" s="31" t="e">
+      <c r="AW6" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX6" s="31" t="e">
+      <c r="AX6" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY6" s="31" t="e">
+      <c r="AY6" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ6" s="30" t="e">
+      <c r="AZ6" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA6" s="30" t="e">
+      <c r="BA6" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB6" s="30" t="e">
+      <c r="BB6" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC6" s="30" t="e">
+      <c r="BC6" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD6" s="31" t="e">
+      <c r="BD6" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE6" s="31" t="e">
+      <c r="BE6" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF6" s="31" t="e">
+      <c r="BF6" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG6" s="31" t="e">
+      <c r="BG6" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH6" s="31" t="e">
+      <c r="BH6" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI6" s="31" t="e">
+      <c r="BI6" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="7" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C7" s="4" t="s">
         <v>66</v>
       </c>
@@ -3065,175 +3049,175 @@
       <c r="Q7" s="16">
         <v>350</v>
       </c>
-      <c r="T7" s="30">
+      <c r="T7" s="22">
         <v>-18</v>
       </c>
-      <c r="U7" s="31" t="e">
+      <c r="U7" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V7" s="31" t="e">
+      <c r="V7" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W7" s="31" t="e">
+      <c r="W7" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X7" s="31" t="e">
+      <c r="X7" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y7" s="31" t="e">
+      <c r="Y7" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z7" s="31" t="e">
+      <c r="Z7" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA7" s="31" t="e">
+      <c r="AA7" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB7" s="31" t="e">
+      <c r="AB7" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC7" s="31" t="e">
+      <c r="AC7" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD7" s="31" t="e">
+      <c r="AD7" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE7" s="31" t="e">
+      <c r="AE7" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF7" s="31" t="e">
+      <c r="AF7" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG7" s="31" t="e">
+      <c r="AG7" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH7" s="31" t="e">
+      <c r="AH7" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI7" s="31">
+      <c r="AI7" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ7" s="31" t="e">
+      <c r="AJ7" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK7" s="31" t="e">
+      <c r="AK7" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL7" s="31" t="e">
+      <c r="AL7" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM7" s="31" t="e">
+      <c r="AM7" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN7" s="31" t="e">
+      <c r="AN7" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO7" s="31" t="e">
+      <c r="AO7" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP7" s="31" t="e">
+      <c r="AP7" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ7" s="31" t="e">
+      <c r="AQ7" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR7" s="31" t="e">
+      <c r="AR7" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS7" s="31" t="e">
+      <c r="AS7" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT7" s="31" t="e">
+      <c r="AT7" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU7" s="31" t="e">
+      <c r="AU7" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV7" s="31" t="e">
+      <c r="AV7" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW7" s="31" t="e">
+      <c r="AW7" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX7" s="31" t="e">
+      <c r="AX7" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY7" s="31" t="e">
+      <c r="AY7" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ7" s="30" t="e">
+      <c r="AZ7" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA7" s="30" t="e">
+      <c r="BA7" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB7" s="30" t="e">
+      <c r="BB7" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC7" s="30" t="e">
+      <c r="BC7" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD7" s="31" t="e">
+      <c r="BD7" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE7" s="31" t="e">
+      <c r="BE7" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF7" s="31" t="e">
+      <c r="BF7" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG7" s="31" t="e">
+      <c r="BG7" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH7" s="31" t="e">
+      <c r="BH7" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI7" s="31" t="e">
+      <c r="BI7" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="8" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C8" s="4" t="s">
         <v>71</v>
       </c>
@@ -3271,175 +3255,175 @@
       <c r="Q8" s="16">
         <v>2180</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="22">
         <v>-17</v>
       </c>
-      <c r="U8" s="31" t="e">
+      <c r="U8" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V8" s="31" t="e">
+      <c r="V8" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W8" s="31" t="e">
+      <c r="W8" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X8" s="31" t="e">
+      <c r="X8" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y8" s="31" t="e">
+      <c r="Y8" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z8" s="31" t="e">
+      <c r="Z8" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA8" s="31" t="e">
+      <c r="AA8" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB8" s="31" t="e">
+      <c r="AB8" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC8" s="31" t="e">
+      <c r="AC8" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD8" s="31" t="e">
+      <c r="AD8" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE8" s="31" t="e">
+      <c r="AE8" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF8" s="31" t="e">
+      <c r="AF8" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG8" s="31" t="e">
+      <c r="AG8" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH8" s="31" t="e">
+      <c r="AH8" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI8" s="31">
+      <c r="AI8" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ8" s="31" t="e">
+      <c r="AJ8" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK8" s="31" t="e">
+      <c r="AK8" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL8" s="31" t="e">
+      <c r="AL8" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM8" s="31" t="e">
+      <c r="AM8" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN8" s="31" t="e">
+      <c r="AN8" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO8" s="31" t="e">
+      <c r="AO8" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP8" s="31" t="e">
+      <c r="AP8" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ8" s="31" t="e">
+      <c r="AQ8" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR8" s="31" t="e">
+      <c r="AR8" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS8" s="31" t="e">
+      <c r="AS8" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT8" s="31" t="e">
+      <c r="AT8" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU8" s="31" t="e">
+      <c r="AU8" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV8" s="31" t="e">
+      <c r="AV8" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW8" s="31" t="e">
+      <c r="AW8" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX8" s="31" t="e">
+      <c r="AX8" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY8" s="31" t="e">
+      <c r="AY8" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ8" s="30" t="e">
+      <c r="AZ8" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA8" s="30" t="e">
+      <c r="BA8" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB8" s="30" t="e">
+      <c r="BB8" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC8" s="30" t="e">
+      <c r="BC8" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD8" s="31" t="e">
+      <c r="BD8" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE8" s="31" t="e">
+      <c r="BE8" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF8" s="31" t="e">
+      <c r="BF8" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG8" s="31" t="e">
+      <c r="BG8" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH8" s="31" t="e">
+      <c r="BH8" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI8" s="31" t="e">
+      <c r="BI8" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="9" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>76</v>
       </c>
@@ -3475,175 +3459,175 @@
       <c r="Q9" s="16">
         <v>274</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="22">
         <v>-16</v>
       </c>
-      <c r="U9" s="31" t="e">
+      <c r="U9" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V9" s="31" t="e">
+      <c r="V9" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W9" s="31" t="e">
+      <c r="W9" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X9" s="31" t="e">
+      <c r="X9" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y9" s="31" t="e">
+      <c r="Y9" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z9" s="31" t="e">
+      <c r="Z9" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA9" s="31" t="e">
+      <c r="AA9" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB9" s="31" t="e">
+      <c r="AB9" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC9" s="31" t="e">
+      <c r="AC9" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD9" s="31" t="e">
+      <c r="AD9" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE9" s="31" t="e">
+      <c r="AE9" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF9" s="31" t="e">
+      <c r="AF9" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG9" s="31" t="e">
+      <c r="AG9" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH9" s="31" t="e">
+      <c r="AH9" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI9" s="31">
+      <c r="AI9" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ9" s="31" t="e">
+      <c r="AJ9" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK9" s="31" t="e">
+      <c r="AK9" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL9" s="31" t="e">
+      <c r="AL9" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM9" s="31" t="e">
+      <c r="AM9" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN9" s="31" t="e">
+      <c r="AN9" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO9" s="31" t="e">
+      <c r="AO9" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP9" s="31" t="e">
+      <c r="AP9" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ9" s="31" t="e">
+      <c r="AQ9" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR9" s="31" t="e">
+      <c r="AR9" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS9" s="31" t="e">
+      <c r="AS9" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT9" s="31" t="e">
+      <c r="AT9" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU9" s="31" t="e">
+      <c r="AU9" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV9" s="31" t="e">
+      <c r="AV9" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW9" s="31" t="e">
+      <c r="AW9" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX9" s="31" t="e">
+      <c r="AX9" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY9" s="31" t="e">
+      <c r="AY9" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ9" s="30" t="e">
+      <c r="AZ9" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA9" s="30" t="e">
+      <c r="BA9" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB9" s="30" t="e">
+      <c r="BB9" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC9" s="30" t="e">
+      <c r="BC9" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD9" s="31" t="e">
+      <c r="BD9" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE9" s="31" t="e">
+      <c r="BE9" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF9" s="31" t="e">
+      <c r="BF9" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG9" s="31" t="e">
+      <c r="BG9" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH9" s="31" t="e">
+      <c r="BH9" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI9" s="31" t="e">
+      <c r="BI9" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="10" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C10" s="4" t="s">
         <v>81</v>
       </c>
@@ -3679,175 +3663,175 @@
       <c r="Q10" s="16">
         <v>350</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10" s="22">
         <v>-15</v>
       </c>
-      <c r="U10" s="31" t="e">
+      <c r="U10" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V10" s="31" t="e">
+      <c r="V10" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W10" s="31" t="e">
+      <c r="W10" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X10" s="31" t="e">
+      <c r="X10" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y10" s="31" t="e">
+      <c r="Y10" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z10" s="31" t="e">
+      <c r="Z10" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA10" s="31" t="e">
+      <c r="AA10" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB10" s="31" t="e">
+      <c r="AB10" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC10" s="31" t="e">
+      <c r="AC10" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD10" s="31" t="e">
+      <c r="AD10" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE10" s="31" t="e">
+      <c r="AE10" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF10" s="31" t="e">
+      <c r="AF10" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG10" s="31" t="e">
+      <c r="AG10" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH10" s="31" t="e">
+      <c r="AH10" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI10" s="31">
+      <c r="AI10" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ10" s="31" t="e">
+      <c r="AJ10" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK10" s="31" t="e">
+      <c r="AK10" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL10" s="31" t="e">
+      <c r="AL10" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM10" s="31" t="e">
+      <c r="AM10" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN10" s="31" t="e">
+      <c r="AN10" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO10" s="31" t="e">
+      <c r="AO10" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP10" s="31" t="e">
+      <c r="AP10" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ10" s="31" t="e">
+      <c r="AQ10" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR10" s="31" t="e">
+      <c r="AR10" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS10" s="31" t="e">
+      <c r="AS10" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT10" s="31" t="e">
+      <c r="AT10" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU10" s="31" t="e">
+      <c r="AU10" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV10" s="31" t="e">
+      <c r="AV10" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW10" s="31" t="e">
+      <c r="AW10" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX10" s="31" t="e">
+      <c r="AX10" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY10" s="31" t="e">
+      <c r="AY10" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ10" s="30" t="e">
+      <c r="AZ10" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA10" s="30" t="e">
+      <c r="BA10" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB10" s="30" t="e">
+      <c r="BB10" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC10" s="30" t="e">
+      <c r="BC10" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD10" s="31" t="e">
+      <c r="BD10" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE10" s="31" t="e">
+      <c r="BE10" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF10" s="31" t="e">
+      <c r="BF10" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG10" s="31" t="e">
+      <c r="BG10" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH10" s="31" t="e">
+      <c r="BH10" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI10" s="31" t="e">
+      <c r="BI10" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="11" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
         <v>86</v>
       </c>
@@ -3883,175 +3867,175 @@
       <c r="Q11" s="16">
         <v>2440</v>
       </c>
-      <c r="T11" s="30">
+      <c r="T11" s="22">
         <v>-14</v>
       </c>
-      <c r="U11" s="31" t="e">
+      <c r="U11" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V11" s="31" t="e">
+      <c r="V11" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W11" s="31" t="e">
+      <c r="W11" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X11" s="31" t="e">
+      <c r="X11" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y11" s="31" t="e">
+      <c r="Y11" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z11" s="31" t="e">
+      <c r="Z11" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA11" s="31" t="e">
+      <c r="AA11" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB11" s="31" t="e">
+      <c r="AB11" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC11" s="31" t="e">
+      <c r="AC11" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD11" s="31" t="e">
+      <c r="AD11" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE11" s="31" t="e">
+      <c r="AE11" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF11" s="31" t="e">
+      <c r="AF11" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG11" s="31" t="e">
+      <c r="AG11" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH11" s="31" t="e">
+      <c r="AH11" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI11" s="31">
+      <c r="AI11" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ11" s="31" t="e">
+      <c r="AJ11" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK11" s="31" t="e">
+      <c r="AK11" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL11" s="31" t="e">
+      <c r="AL11" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM11" s="31" t="e">
+      <c r="AM11" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN11" s="31" t="e">
+      <c r="AN11" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO11" s="31" t="e">
+      <c r="AO11" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP11" s="31" t="e">
+      <c r="AP11" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ11" s="31" t="e">
+      <c r="AQ11" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR11" s="31" t="e">
+      <c r="AR11" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS11" s="31" t="e">
+      <c r="AS11" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT11" s="31" t="e">
+      <c r="AT11" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU11" s="31" t="e">
+      <c r="AU11" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV11" s="31" t="e">
+      <c r="AV11" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW11" s="31" t="e">
+      <c r="AW11" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX11" s="31" t="e">
+      <c r="AX11" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY11" s="31" t="e">
+      <c r="AY11" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ11" s="30" t="e">
+      <c r="AZ11" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA11" s="30" t="e">
+      <c r="BA11" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB11" s="30" t="e">
+      <c r="BB11" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC11" s="30" t="e">
+      <c r="BC11" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD11" s="31" t="e">
+      <c r="BD11" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE11" s="31" t="e">
+      <c r="BE11" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF11" s="31" t="e">
+      <c r="BF11" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG11" s="31" t="e">
+      <c r="BG11" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH11" s="31" t="e">
+      <c r="BH11" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI11" s="31" t="e">
+      <c r="BI11" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="12" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C12" s="4" t="s">
         <v>92</v>
       </c>
@@ -4074,175 +4058,175 @@
       <c r="K12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="22">
         <v>-13</v>
       </c>
-      <c r="U12" s="31" t="e">
+      <c r="U12" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V12" s="31" t="e">
+      <c r="V12" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W12" s="31" t="e">
+      <c r="W12" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X12" s="31" t="e">
+      <c r="X12" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y12" s="31" t="e">
+      <c r="Y12" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z12" s="31" t="e">
+      <c r="Z12" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA12" s="31" t="e">
+      <c r="AA12" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB12" s="31" t="e">
+      <c r="AB12" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC12" s="31" t="e">
+      <c r="AC12" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD12" s="31" t="e">
+      <c r="AD12" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE12" s="31" t="e">
+      <c r="AE12" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF12" s="31" t="e">
+      <c r="AF12" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG12" s="31" t="e">
+      <c r="AG12" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH12" s="31" t="e">
+      <c r="AH12" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI12" s="31">
+      <c r="AI12" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="31" t="e">
+      <c r="AJ12" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK12" s="31" t="e">
+      <c r="AK12" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL12" s="31" t="e">
+      <c r="AL12" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM12" s="31" t="e">
+      <c r="AM12" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN12" s="31" t="e">
+      <c r="AN12" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO12" s="31" t="e">
+      <c r="AO12" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP12" s="31" t="e">
+      <c r="AP12" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ12" s="31" t="e">
+      <c r="AQ12" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR12" s="31" t="e">
+      <c r="AR12" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS12" s="31" t="e">
+      <c r="AS12" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT12" s="31" t="e">
+      <c r="AT12" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU12" s="31" t="e">
+      <c r="AU12" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV12" s="31" t="e">
+      <c r="AV12" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW12" s="31" t="e">
+      <c r="AW12" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX12" s="31" t="e">
+      <c r="AX12" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY12" s="31" t="e">
+      <c r="AY12" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ12" s="30" t="e">
+      <c r="AZ12" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA12" s="30" t="e">
+      <c r="BA12" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB12" s="30" t="e">
+      <c r="BB12" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC12" s="30" t="e">
+      <c r="BC12" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD12" s="31" t="e">
+      <c r="BD12" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE12" s="31" t="e">
+      <c r="BE12" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF12" s="31" t="e">
+      <c r="BF12" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG12" s="31" t="e">
+      <c r="BG12" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH12" s="31" t="e">
+      <c r="BH12" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI12" s="31" t="e">
+      <c r="BI12" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="13" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C13" s="4" t="s">
         <v>97</v>
       </c>
@@ -4255,182 +4239,182 @@
       <c r="F13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="21"/>
-      <c r="T13" s="30">
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="29"/>
+      <c r="T13" s="22">
         <v>-12</v>
       </c>
-      <c r="U13" s="31" t="e">
+      <c r="U13" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V13" s="31" t="e">
+      <c r="V13" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W13" s="31" t="e">
+      <c r="W13" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X13" s="31" t="e">
+      <c r="X13" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y13" s="31" t="e">
+      <c r="Y13" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z13" s="31" t="e">
+      <c r="Z13" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA13" s="31" t="e">
+      <c r="AA13" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB13" s="31" t="e">
+      <c r="AB13" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC13" s="31" t="e">
+      <c r="AC13" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD13" s="31" t="e">
+      <c r="AD13" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE13" s="31" t="e">
+      <c r="AE13" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF13" s="31" t="e">
+      <c r="AF13" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG13" s="31" t="e">
+      <c r="AG13" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH13" s="31" t="e">
+      <c r="AH13" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI13" s="31">
+      <c r="AI13" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ13" s="31" t="e">
+      <c r="AJ13" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK13" s="31" t="e">
+      <c r="AK13" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL13" s="31" t="e">
+      <c r="AL13" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM13" s="31" t="e">
+      <c r="AM13" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN13" s="31" t="e">
+      <c r="AN13" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO13" s="31" t="e">
+      <c r="AO13" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP13" s="31" t="e">
+      <c r="AP13" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ13" s="31" t="e">
+      <c r="AQ13" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR13" s="31" t="e">
+      <c r="AR13" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS13" s="31" t="e">
+      <c r="AS13" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT13" s="31" t="e">
+      <c r="AT13" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU13" s="31" t="e">
+      <c r="AU13" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV13" s="31" t="e">
+      <c r="AV13" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW13" s="31" t="e">
+      <c r="AW13" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX13" s="31" t="e">
+      <c r="AX13" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY13" s="31" t="e">
+      <c r="AY13" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ13" s="30" t="e">
+      <c r="AZ13" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA13" s="30" t="e">
+      <c r="BA13" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB13" s="30" t="e">
+      <c r="BB13" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC13" s="30" t="e">
+      <c r="BC13" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD13" s="31" t="e">
+      <c r="BD13" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE13" s="31" t="e">
+      <c r="BE13" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF13" s="31" t="e">
+      <c r="BF13" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG13" s="31" t="e">
+      <c r="BG13" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH13" s="31" t="e">
+      <c r="BH13" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI13" s="31" t="e">
+      <c r="BI13" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="14" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C14" s="4" t="s">
         <v>100</v>
       </c>
@@ -4443,188 +4427,188 @@
       <c r="F14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="21"/>
-      <c r="M14" s="24">
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+      <c r="M14" s="34">
         <v>0</v>
       </c>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="21"/>
-      <c r="T14" s="30">
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="29"/>
+      <c r="T14" s="22">
         <v>-11</v>
       </c>
-      <c r="U14" s="31" t="e">
+      <c r="U14" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V14" s="31" t="e">
+      <c r="V14" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W14" s="31" t="e">
+      <c r="W14" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X14" s="31" t="e">
+      <c r="X14" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y14" s="31" t="e">
+      <c r="Y14" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z14" s="31" t="e">
+      <c r="Z14" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA14" s="31" t="e">
+      <c r="AA14" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB14" s="31" t="e">
+      <c r="AB14" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC14" s="31" t="e">
+      <c r="AC14" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD14" s="31" t="e">
+      <c r="AD14" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE14" s="31" t="e">
+      <c r="AE14" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF14" s="31" t="e">
+      <c r="AF14" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG14" s="31" t="e">
+      <c r="AG14" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH14" s="31" t="e">
+      <c r="AH14" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI14" s="31">
+      <c r="AI14" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="31" t="e">
+      <c r="AJ14" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK14" s="31" t="e">
+      <c r="AK14" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL14" s="31" t="e">
+      <c r="AL14" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM14" s="31" t="e">
+      <c r="AM14" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN14" s="31" t="e">
+      <c r="AN14" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO14" s="31" t="e">
+      <c r="AO14" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP14" s="31" t="e">
+      <c r="AP14" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ14" s="31" t="e">
+      <c r="AQ14" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR14" s="31" t="e">
+      <c r="AR14" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS14" s="31" t="e">
+      <c r="AS14" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT14" s="31" t="e">
+      <c r="AT14" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU14" s="31" t="e">
+      <c r="AU14" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV14" s="31" t="e">
+      <c r="AV14" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW14" s="31" t="e">
+      <c r="AW14" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX14" s="31" t="e">
+      <c r="AX14" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY14" s="31" t="e">
+      <c r="AY14" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ14" s="30" t="e">
+      <c r="AZ14" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA14" s="30" t="e">
+      <c r="BA14" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB14" s="30" t="e">
+      <c r="BB14" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC14" s="30" t="e">
+      <c r="BC14" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD14" s="31" t="e">
+      <c r="BD14" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE14" s="31" t="e">
+      <c r="BE14" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF14" s="31" t="e">
+      <c r="BF14" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG14" s="31" t="e">
+      <c r="BG14" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH14" s="31" t="e">
+      <c r="BH14" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI14" s="31" t="e">
+      <c r="BI14" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="15" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C15" s="4" t="s">
         <v>103</v>
       </c>
@@ -4649,175 +4633,175 @@
       <c r="K15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T15" s="30">
+      <c r="T15" s="22">
         <v>-10</v>
       </c>
-      <c r="U15" s="31" t="e">
+      <c r="U15" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V15" s="31" t="e">
+      <c r="V15" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W15" s="31" t="e">
+      <c r="W15" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X15" s="31" t="e">
+      <c r="X15" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y15" s="31" t="e">
+      <c r="Y15" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z15" s="31" t="e">
+      <c r="Z15" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA15" s="31" t="e">
+      <c r="AA15" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB15" s="31" t="e">
+      <c r="AB15" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC15" s="31" t="e">
+      <c r="AC15" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD15" s="31" t="e">
+      <c r="AD15" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE15" s="31" t="e">
+      <c r="AE15" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF15" s="31" t="e">
+      <c r="AF15" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG15" s="31" t="e">
+      <c r="AG15" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH15" s="31" t="e">
+      <c r="AH15" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI15" s="31">
+      <c r="AI15" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ15" s="31" t="e">
+      <c r="AJ15" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK15" s="31" t="e">
+      <c r="AK15" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL15" s="31" t="e">
+      <c r="AL15" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM15" s="31" t="e">
+      <c r="AM15" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN15" s="31" t="e">
+      <c r="AN15" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO15" s="31" t="e">
+      <c r="AO15" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP15" s="31" t="e">
+      <c r="AP15" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ15" s="31" t="e">
+      <c r="AQ15" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR15" s="31" t="e">
+      <c r="AR15" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS15" s="31" t="e">
+      <c r="AS15" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT15" s="31" t="e">
+      <c r="AT15" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU15" s="31" t="e">
+      <c r="AU15" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV15" s="31" t="e">
+      <c r="AV15" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW15" s="31" t="e">
+      <c r="AW15" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX15" s="31" t="e">
+      <c r="AX15" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY15" s="31" t="e">
+      <c r="AY15" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ15" s="30" t="e">
+      <c r="AZ15" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA15" s="30" t="e">
+      <c r="BA15" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB15" s="30" t="e">
+      <c r="BB15" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC15" s="30" t="e">
+      <c r="BC15" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD15" s="31" t="e">
+      <c r="BD15" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE15" s="31" t="e">
+      <c r="BE15" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF15" s="31" t="e">
+      <c r="BF15" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG15" s="31" t="e">
+      <c r="BG15" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH15" s="31" t="e">
+      <c r="BH15" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI15" s="31" t="e">
+      <c r="BI15" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="16" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
@@ -4842,175 +4826,175 @@
       <c r="K16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="T16" s="30">
+      <c r="T16" s="22">
         <v>-9</v>
       </c>
-      <c r="U16" s="31" t="e">
+      <c r="U16" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V16" s="31" t="e">
+      <c r="V16" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W16" s="31" t="e">
+      <c r="W16" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X16" s="31" t="e">
+      <c r="X16" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y16" s="31" t="e">
+      <c r="Y16" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z16" s="31" t="e">
+      <c r="Z16" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA16" s="31" t="e">
+      <c r="AA16" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB16" s="31" t="e">
+      <c r="AB16" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC16" s="31" t="e">
+      <c r="AC16" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD16" s="31" t="e">
+      <c r="AD16" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE16" s="31" t="e">
+      <c r="AE16" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF16" s="31" t="e">
+      <c r="AF16" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG16" s="31" t="e">
+      <c r="AG16" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH16" s="31" t="e">
+      <c r="AH16" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI16" s="31">
+      <c r="AI16" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="31" t="e">
+      <c r="AJ16" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK16" s="31" t="e">
+      <c r="AK16" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL16" s="31" t="e">
+      <c r="AL16" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM16" s="31" t="e">
+      <c r="AM16" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN16" s="31" t="e">
+      <c r="AN16" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO16" s="31" t="e">
+      <c r="AO16" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP16" s="31" t="e">
+      <c r="AP16" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ16" s="31" t="e">
+      <c r="AQ16" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR16" s="31" t="e">
+      <c r="AR16" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS16" s="31" t="e">
+      <c r="AS16" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT16" s="31" t="e">
+      <c r="AT16" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU16" s="31" t="e">
+      <c r="AU16" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV16" s="31" t="e">
+      <c r="AV16" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW16" s="31" t="e">
+      <c r="AW16" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX16" s="31" t="e">
+      <c r="AX16" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY16" s="31" t="e">
+      <c r="AY16" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ16" s="30" t="e">
+      <c r="AZ16" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA16" s="30" t="e">
+      <c r="BA16" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB16" s="30" t="e">
+      <c r="BB16" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC16" s="30" t="e">
+      <c r="BC16" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD16" s="31" t="e">
+      <c r="BD16" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE16" s="31" t="e">
+      <c r="BE16" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF16" s="31" t="e">
+      <c r="BF16" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG16" s="31" t="e">
+      <c r="BG16" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH16" s="31" t="e">
+      <c r="BH16" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI16" s="31" t="e">
+      <c r="BI16" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="17" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H17" s="5" t="s">
         <v>109</v>
       </c>
@@ -5024,181 +5008,181 @@
       <c r="K17" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="T17" s="30">
+      <c r="T17" s="22">
         <v>-8</v>
       </c>
-      <c r="U17" s="31" t="e">
+      <c r="U17" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V17" s="31" t="e">
+      <c r="V17" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W17" s="31" t="e">
+      <c r="W17" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X17" s="31" t="e">
+      <c r="X17" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y17" s="31" t="e">
+      <c r="Y17" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z17" s="31" t="e">
+      <c r="Z17" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA17" s="31" t="e">
+      <c r="AA17" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB17" s="31" t="e">
+      <c r="AB17" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC17" s="31" t="e">
+      <c r="AC17" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD17" s="31" t="e">
+      <c r="AD17" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE17" s="31" t="e">
+      <c r="AE17" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF17" s="31" t="e">
+      <c r="AF17" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG17" s="31" t="e">
+      <c r="AG17" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH17" s="31" t="e">
+      <c r="AH17" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI17" s="31">
+      <c r="AI17" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="31" t="e">
+      <c r="AJ17" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK17" s="31" t="e">
+      <c r="AK17" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL17" s="31" t="e">
+      <c r="AL17" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM17" s="31" t="e">
+      <c r="AM17" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN17" s="31" t="e">
+      <c r="AN17" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO17" s="31" t="e">
+      <c r="AO17" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP17" s="31" t="e">
+      <c r="AP17" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ17" s="31" t="e">
+      <c r="AQ17" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR17" s="31" t="e">
+      <c r="AR17" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS17" s="31" t="e">
+      <c r="AS17" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT17" s="31" t="e">
+      <c r="AT17" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU17" s="31" t="e">
+      <c r="AU17" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV17" s="31" t="e">
+      <c r="AV17" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW17" s="31" t="e">
+      <c r="AW17" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX17" s="31" t="e">
+      <c r="AX17" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY17" s="31" t="e">
+      <c r="AY17" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ17" s="30" t="e">
+      <c r="AZ17" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA17" s="30" t="e">
+      <c r="BA17" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB17" s="30" t="e">
+      <c r="BB17" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC17" s="30" t="e">
+      <c r="BC17" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD17" s="31" t="e">
+      <c r="BD17" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE17" s="31" t="e">
+      <c r="BE17" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF17" s="31" t="e">
+      <c r="BF17" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG17" s="31" t="e">
+      <c r="BG17" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH17" s="31" t="e">
+      <c r="BH17" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI17" s="31" t="e">
+      <c r="BI17" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="18" spans="3:61" x14ac:dyDescent="0.25">
-      <c r="C18" s="19" t="s">
+    <row r="18" spans="3:61" x14ac:dyDescent="0.3">
+      <c r="C18" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
       <c r="H18" s="5" t="s">
         <v>112</v>
       </c>
@@ -5212,175 +5196,175 @@
       <c r="K18" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="T18" s="30">
+      <c r="T18" s="22">
         <v>-7</v>
       </c>
-      <c r="U18" s="31" t="e">
+      <c r="U18" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V18" s="31" t="e">
+      <c r="V18" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W18" s="31" t="e">
+      <c r="W18" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X18" s="31" t="e">
+      <c r="X18" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y18" s="31" t="e">
+      <c r="Y18" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z18" s="31" t="e">
+      <c r="Z18" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA18" s="31" t="e">
+      <c r="AA18" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB18" s="31" t="e">
+      <c r="AB18" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC18" s="31" t="e">
+      <c r="AC18" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD18" s="31" t="e">
+      <c r="AD18" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE18" s="31" t="e">
+      <c r="AE18" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF18" s="31" t="e">
+      <c r="AF18" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG18" s="31" t="e">
+      <c r="AG18" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH18" s="31" t="e">
+      <c r="AH18" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI18" s="31">
+      <c r="AI18" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="31" t="e">
+      <c r="AJ18" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK18" s="31" t="e">
+      <c r="AK18" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL18" s="31" t="e">
+      <c r="AL18" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM18" s="31" t="e">
+      <c r="AM18" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN18" s="31" t="e">
+      <c r="AN18" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO18" s="31" t="e">
+      <c r="AO18" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP18" s="31" t="e">
+      <c r="AP18" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ18" s="31" t="e">
+      <c r="AQ18" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR18" s="31" t="e">
+      <c r="AR18" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS18" s="31" t="e">
+      <c r="AS18" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT18" s="31" t="e">
+      <c r="AT18" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU18" s="31" t="e">
+      <c r="AU18" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV18" s="31" t="e">
+      <c r="AV18" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW18" s="31" t="e">
+      <c r="AW18" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX18" s="31" t="e">
+      <c r="AX18" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY18" s="31" t="e">
+      <c r="AY18" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ18" s="30" t="e">
+      <c r="AZ18" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA18" s="30" t="e">
+      <c r="BA18" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB18" s="30" t="e">
+      <c r="BB18" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC18" s="30" t="e">
+      <c r="BC18" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD18" s="31" t="e">
+      <c r="BD18" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE18" s="31" t="e">
+      <c r="BE18" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF18" s="31" t="e">
+      <c r="BF18" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG18" s="31" t="e">
+      <c r="BG18" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH18" s="31" t="e">
+      <c r="BH18" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI18" s="31" t="e">
+      <c r="BI18" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="19" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>105</v>
       </c>
@@ -5406,175 +5390,175 @@
       <c r="K19" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="T19" s="30">
+      <c r="T19" s="22">
         <v>-6</v>
       </c>
-      <c r="U19" s="31" t="e">
+      <c r="U19" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V19" s="31" t="e">
+      <c r="V19" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W19" s="31" t="e">
+      <c r="W19" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X19" s="31" t="e">
+      <c r="X19" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y19" s="31" t="e">
+      <c r="Y19" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z19" s="31" t="e">
+      <c r="Z19" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA19" s="31" t="e">
+      <c r="AA19" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB19" s="31" t="e">
+      <c r="AB19" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC19" s="31" t="e">
+      <c r="AC19" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD19" s="31" t="e">
+      <c r="AD19" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE19" s="31" t="e">
+      <c r="AE19" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF19" s="31" t="e">
+      <c r="AF19" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG19" s="31" t="e">
+      <c r="AG19" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH19" s="31" t="e">
+      <c r="AH19" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI19" s="31">
+      <c r="AI19" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ19" s="31" t="e">
+      <c r="AJ19" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK19" s="31" t="e">
+      <c r="AK19" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL19" s="31" t="e">
+      <c r="AL19" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM19" s="31" t="e">
+      <c r="AM19" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN19" s="31" t="e">
+      <c r="AN19" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO19" s="31" t="e">
+      <c r="AO19" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP19" s="31" t="e">
+      <c r="AP19" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ19" s="31" t="e">
+      <c r="AQ19" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR19" s="31" t="e">
+      <c r="AR19" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS19" s="31" t="e">
+      <c r="AS19" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT19" s="31" t="e">
+      <c r="AT19" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU19" s="31" t="e">
+      <c r="AU19" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV19" s="31" t="e">
+      <c r="AV19" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW19" s="31" t="e">
+      <c r="AW19" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX19" s="31" t="e">
+      <c r="AX19" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY19" s="31" t="e">
+      <c r="AY19" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ19" s="30" t="e">
+      <c r="AZ19" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA19" s="30" t="e">
+      <c r="BA19" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB19" s="30" t="e">
+      <c r="BB19" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC19" s="30" t="e">
+      <c r="BC19" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD19" s="31" t="e">
+      <c r="BD19" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE19" s="31" t="e">
+      <c r="BE19" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF19" s="31" t="e">
+      <c r="BF19" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG19" s="31" t="e">
+      <c r="BG19" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH19" s="31" t="e">
+      <c r="BH19" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI19" s="31" t="e">
+      <c r="BI19" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="20" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C20" s="3" t="s">
         <v>115</v>
       </c>
@@ -5601,175 +5585,175 @@
       <c r="K20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="T20" s="30">
+      <c r="T20" s="22">
         <v>-5</v>
       </c>
-      <c r="U20" s="31" t="e">
+      <c r="U20" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V20" s="31" t="e">
+      <c r="V20" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W20" s="31" t="e">
+      <c r="W20" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X20" s="31" t="e">
+      <c r="X20" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y20" s="31" t="e">
+      <c r="Y20" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z20" s="31" t="e">
+      <c r="Z20" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA20" s="31" t="e">
+      <c r="AA20" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB20" s="31" t="e">
+      <c r="AB20" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC20" s="31" t="e">
+      <c r="AC20" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD20" s="31" t="e">
+      <c r="AD20" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE20" s="31" t="e">
+      <c r="AE20" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF20" s="31" t="e">
+      <c r="AF20" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG20" s="31" t="e">
+      <c r="AG20" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH20" s="31" t="e">
+      <c r="AH20" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI20" s="31">
+      <c r="AI20" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ20" s="31" t="e">
+      <c r="AJ20" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK20" s="31" t="e">
+      <c r="AK20" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL20" s="31" t="e">
+      <c r="AL20" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM20" s="31" t="e">
+      <c r="AM20" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN20" s="31" t="e">
+      <c r="AN20" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO20" s="31" t="e">
+      <c r="AO20" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP20" s="31" t="e">
+      <c r="AP20" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ20" s="31" t="e">
+      <c r="AQ20" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR20" s="31" t="e">
+      <c r="AR20" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS20" s="31" t="e">
+      <c r="AS20" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT20" s="31" t="e">
+      <c r="AT20" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU20" s="31" t="e">
+      <c r="AU20" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV20" s="31" t="e">
+      <c r="AV20" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW20" s="31" t="e">
+      <c r="AW20" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX20" s="31" t="e">
+      <c r="AX20" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY20" s="31" t="e">
+      <c r="AY20" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ20" s="30" t="e">
+      <c r="AZ20" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA20" s="30" t="e">
+      <c r="BA20" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB20" s="30" t="e">
+      <c r="BB20" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC20" s="30" t="e">
+      <c r="BC20" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD20" s="31" t="e">
+      <c r="BD20" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE20" s="31" t="e">
+      <c r="BE20" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF20" s="31" t="e">
+      <c r="BF20" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG20" s="31" t="e">
+      <c r="BG20" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH20" s="31" t="e">
+      <c r="BH20" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI20" s="31" t="e">
+      <c r="BI20" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="21" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C21" s="3" t="s">
         <v>119</v>
       </c>
@@ -5796,175 +5780,175 @@
       <c r="K21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="22">
         <v>-4</v>
       </c>
-      <c r="U21" s="31" t="e">
+      <c r="U21" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V21" s="31" t="e">
+      <c r="V21" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W21" s="31" t="e">
+      <c r="W21" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X21" s="31" t="e">
+      <c r="X21" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y21" s="31" t="e">
+      <c r="Y21" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z21" s="31" t="e">
+      <c r="Z21" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA21" s="31" t="e">
+      <c r="AA21" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB21" s="31" t="e">
+      <c r="AB21" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC21" s="31" t="e">
+      <c r="AC21" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD21" s="31" t="e">
+      <c r="AD21" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE21" s="31" t="e">
+      <c r="AE21" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF21" s="31" t="e">
+      <c r="AF21" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG21" s="31" t="e">
+      <c r="AG21" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH21" s="31" t="e">
+      <c r="AH21" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI21" s="31">
+      <c r="AI21" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ21" s="31" t="e">
+      <c r="AJ21" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK21" s="31" t="e">
+      <c r="AK21" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL21" s="31" t="e">
+      <c r="AL21" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM21" s="31" t="e">
+      <c r="AM21" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN21" s="31" t="e">
+      <c r="AN21" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO21" s="31" t="e">
+      <c r="AO21" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP21" s="31" t="e">
+      <c r="AP21" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ21" s="31" t="e">
+      <c r="AQ21" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR21" s="31" t="e">
+      <c r="AR21" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS21" s="31" t="e">
+      <c r="AS21" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT21" s="31" t="e">
+      <c r="AT21" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU21" s="31" t="e">
+      <c r="AU21" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV21" s="31" t="e">
+      <c r="AV21" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW21" s="31" t="e">
+      <c r="AW21" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX21" s="31" t="e">
+      <c r="AX21" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY21" s="31" t="e">
+      <c r="AY21" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ21" s="30" t="e">
+      <c r="AZ21" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA21" s="30" t="e">
+      <c r="BA21" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB21" s="30" t="e">
+      <c r="BB21" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC21" s="30" t="e">
+      <c r="BC21" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD21" s="31" t="e">
+      <c r="BD21" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE21" s="31" t="e">
+      <c r="BE21" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF21" s="31" t="e">
+      <c r="BF21" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG21" s="31" t="e">
+      <c r="BG21" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH21" s="31" t="e">
+      <c r="BH21" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI21" s="31" t="e">
+      <c r="BI21" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="22" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C22" s="3" t="s">
         <v>123</v>
       </c>
@@ -5991,175 +5975,175 @@
       <c r="K22" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="22">
         <v>-3</v>
       </c>
-      <c r="U22" s="31" t="e">
+      <c r="U22" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V22" s="31" t="e">
+      <c r="V22" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W22" s="31" t="e">
+      <c r="W22" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X22" s="31" t="e">
+      <c r="X22" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y22" s="31" t="e">
+      <c r="Y22" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z22" s="31" t="e">
+      <c r="Z22" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA22" s="31" t="e">
+      <c r="AA22" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB22" s="31" t="e">
+      <c r="AB22" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC22" s="31" t="e">
+      <c r="AC22" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD22" s="31" t="e">
+      <c r="AD22" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE22" s="31" t="e">
+      <c r="AE22" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF22" s="31" t="e">
+      <c r="AF22" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG22" s="31" t="e">
+      <c r="AG22" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH22" s="31" t="e">
+      <c r="AH22" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI22" s="31">
+      <c r="AI22" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ22" s="31" t="e">
+      <c r="AJ22" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK22" s="31" t="e">
+      <c r="AK22" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL22" s="31" t="e">
+      <c r="AL22" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM22" s="31" t="e">
+      <c r="AM22" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN22" s="31" t="e">
+      <c r="AN22" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO22" s="31" t="e">
+      <c r="AO22" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP22" s="31" t="e">
+      <c r="AP22" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ22" s="31" t="e">
+      <c r="AQ22" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR22" s="31" t="e">
+      <c r="AR22" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS22" s="31" t="e">
+      <c r="AS22" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT22" s="31" t="e">
+      <c r="AT22" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU22" s="31" t="e">
+      <c r="AU22" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV22" s="31" t="e">
+      <c r="AV22" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW22" s="31" t="e">
+      <c r="AW22" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX22" s="31" t="e">
+      <c r="AX22" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY22" s="31" t="e">
+      <c r="AY22" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ22" s="30" t="e">
+      <c r="AZ22" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA22" s="30" t="e">
+      <c r="BA22" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB22" s="30" t="e">
+      <c r="BB22" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC22" s="30" t="e">
+      <c r="BC22" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD22" s="31" t="e">
+      <c r="BD22" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE22" s="31" t="e">
+      <c r="BE22" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF22" s="31" t="e">
+      <c r="BF22" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG22" s="31" t="e">
+      <c r="BG22" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH22" s="31" t="e">
+      <c r="BH22" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI22" s="31" t="e">
+      <c r="BI22" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="23" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C23" s="3" t="s">
         <v>127</v>
       </c>
@@ -6186,175 +6170,175 @@
       <c r="K23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="T23" s="30">
+      <c r="T23" s="22">
         <v>-2</v>
       </c>
-      <c r="U23" s="31" t="e">
+      <c r="U23" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V23" s="31" t="e">
+      <c r="V23" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W23" s="31" t="e">
+      <c r="W23" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X23" s="31" t="e">
+      <c r="X23" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y23" s="31" t="e">
+      <c r="Y23" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z23" s="31" t="e">
+      <c r="Z23" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA23" s="31" t="e">
+      <c r="AA23" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB23" s="31" t="e">
+      <c r="AB23" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC23" s="31" t="e">
+      <c r="AC23" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD23" s="31" t="e">
+      <c r="AD23" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE23" s="31" t="e">
+      <c r="AE23" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF23" s="31" t="e">
+      <c r="AF23" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG23" s="31" t="e">
+      <c r="AG23" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH23" s="31" t="e">
+      <c r="AH23" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI23" s="31">
+      <c r="AI23" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ23" s="31" t="e">
+      <c r="AJ23" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK23" s="31" t="e">
+      <c r="AK23" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL23" s="31" t="e">
+      <c r="AL23" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM23" s="31" t="e">
+      <c r="AM23" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN23" s="31" t="e">
+      <c r="AN23" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO23" s="31" t="e">
+      <c r="AO23" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP23" s="31" t="e">
+      <c r="AP23" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ23" s="31" t="e">
+      <c r="AQ23" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR23" s="31" t="e">
+      <c r="AR23" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS23" s="31" t="e">
+      <c r="AS23" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT23" s="31" t="e">
+      <c r="AT23" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU23" s="31" t="e">
+      <c r="AU23" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV23" s="31" t="e">
+      <c r="AV23" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW23" s="31" t="e">
+      <c r="AW23" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX23" s="31" t="e">
+      <c r="AX23" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY23" s="31" t="e">
+      <c r="AY23" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ23" s="30" t="e">
+      <c r="AZ23" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA23" s="30" t="e">
+      <c r="BA23" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB23" s="30" t="e">
+      <c r="BB23" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC23" s="30" t="e">
+      <c r="BC23" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD23" s="31" t="e">
+      <c r="BD23" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE23" s="31" t="e">
+      <c r="BE23" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF23" s="31" t="e">
+      <c r="BF23" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG23" s="31" t="e">
+      <c r="BG23" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH23" s="31" t="e">
+      <c r="BH23" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI23" s="31" t="e">
+      <c r="BI23" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="24" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C24" s="3" t="s">
         <v>131</v>
       </c>
@@ -6381,175 +6365,175 @@
       <c r="K24" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="22">
         <v>-1</v>
       </c>
-      <c r="U24" s="31" t="e">
+      <c r="U24" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V24" s="31" t="e">
+      <c r="V24" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W24" s="31" t="e">
+      <c r="W24" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X24" s="31" t="e">
+      <c r="X24" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y24" s="31" t="e">
+      <c r="Y24" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z24" s="31" t="e">
+      <c r="Z24" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA24" s="31" t="e">
+      <c r="AA24" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB24" s="31" t="e">
+      <c r="AB24" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC24" s="31" t="e">
+      <c r="AC24" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD24" s="31" t="e">
+      <c r="AD24" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE24" s="31" t="e">
+      <c r="AE24" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF24" s="31" t="e">
+      <c r="AF24" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG24" s="31" t="e">
+      <c r="AG24" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH24" s="31" t="e">
+      <c r="AH24" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI24" s="31">
+      <c r="AI24" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ24" s="31" t="e">
+      <c r="AJ24" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK24" s="31" t="e">
+      <c r="AK24" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL24" s="31" t="e">
+      <c r="AL24" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM24" s="31" t="e">
+      <c r="AM24" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN24" s="31" t="e">
+      <c r="AN24" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO24" s="31" t="e">
+      <c r="AO24" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP24" s="31" t="e">
+      <c r="AP24" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ24" s="31" t="e">
+      <c r="AQ24" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR24" s="31" t="e">
+      <c r="AR24" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS24" s="31" t="e">
+      <c r="AS24" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT24" s="31" t="e">
+      <c r="AT24" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU24" s="31" t="e">
+      <c r="AU24" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV24" s="31" t="e">
+      <c r="AV24" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW24" s="31" t="e">
+      <c r="AW24" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX24" s="31" t="e">
+      <c r="AX24" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY24" s="31" t="e">
+      <c r="AY24" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ24" s="30" t="e">
+      <c r="AZ24" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA24" s="30" t="e">
+      <c r="BA24" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB24" s="30" t="e">
+      <c r="BB24" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC24" s="30" t="e">
+      <c r="BC24" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD24" s="31" t="e">
+      <c r="BD24" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE24" s="31" t="e">
+      <c r="BE24" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF24" s="31" t="e">
+      <c r="BF24" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG24" s="31" t="e">
+      <c r="BG24" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH24" s="31" t="e">
+      <c r="BH24" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI24" s="31" t="e">
+      <c r="BI24" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="25" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C25" s="3" t="s">
         <v>135</v>
       </c>
@@ -6563,175 +6547,175 @@
       <c r="F25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="22">
         <v>0</v>
       </c>
-      <c r="U25" s="31" t="e">
+      <c r="U25" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V25" s="31" t="e">
+      <c r="V25" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W25" s="31" t="e">
+      <c r="W25" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X25" s="31" t="e">
+      <c r="X25" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y25" s="31" t="e">
+      <c r="Y25" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z25" s="31" t="e">
+      <c r="Z25" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA25" s="31" t="e">
+      <c r="AA25" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB25" s="31" t="e">
+      <c r="AB25" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC25" s="31" t="e">
+      <c r="AC25" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD25" s="31" t="e">
+      <c r="AD25" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE25" s="31" t="e">
+      <c r="AE25" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF25" s="31" t="e">
+      <c r="AF25" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG25" s="31" t="e">
+      <c r="AG25" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH25" s="31" t="e">
+      <c r="AH25" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI25" s="31">
+      <c r="AI25" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ25" s="31" t="e">
+      <c r="AJ25" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK25" s="31" t="e">
+      <c r="AK25" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL25" s="31" t="e">
+      <c r="AL25" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM25" s="31" t="e">
+      <c r="AM25" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN25" s="31" t="e">
+      <c r="AN25" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO25" s="31" t="e">
+      <c r="AO25" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP25" s="31" t="e">
+      <c r="AP25" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ25" s="31" t="e">
+      <c r="AQ25" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR25" s="31" t="e">
+      <c r="AR25" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS25" s="31" t="e">
+      <c r="AS25" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT25" s="31" t="e">
+      <c r="AT25" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU25" s="31" t="e">
+      <c r="AU25" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV25" s="31" t="e">
+      <c r="AV25" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW25" s="31" t="e">
+      <c r="AW25" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX25" s="31" t="e">
+      <c r="AX25" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY25" s="31" t="e">
+      <c r="AY25" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ25" s="30" t="e">
+      <c r="AZ25" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA25" s="30" t="e">
+      <c r="BA25" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB25" s="30" t="e">
+      <c r="BB25" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC25" s="30" t="e">
+      <c r="BC25" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD25" s="31" t="e">
+      <c r="BD25" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE25" s="31" t="e">
+      <c r="BE25" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF25" s="31" t="e">
+      <c r="BF25" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG25" s="31" t="e">
+      <c r="BG25" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH25" s="31" t="e">
+      <c r="BH25" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI25" s="31" t="e">
+      <c r="BI25" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="26" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C26" s="3" t="s">
         <v>137</v>
       </c>
@@ -6745,181 +6729,181 @@
       <c r="F26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H26" s="25" t="s">
+      <c r="H26" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="21"/>
-      <c r="T26" s="30">
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="29"/>
+      <c r="T26" s="22">
         <v>1</v>
       </c>
-      <c r="U26" s="31" t="e">
+      <c r="U26" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V26" s="31" t="e">
+      <c r="V26" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W26" s="31" t="e">
+      <c r="W26" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X26" s="31" t="e">
+      <c r="X26" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y26" s="31" t="e">
+      <c r="Y26" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z26" s="31" t="e">
+      <c r="Z26" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA26" s="31" t="e">
+      <c r="AA26" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB26" s="31" t="e">
+      <c r="AB26" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC26" s="31" t="e">
+      <c r="AC26" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD26" s="31" t="e">
+      <c r="AD26" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE26" s="31" t="e">
+      <c r="AE26" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF26" s="31" t="e">
+      <c r="AF26" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG26" s="31" t="e">
+      <c r="AG26" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH26" s="31" t="e">
+      <c r="AH26" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI26" s="31">
+      <c r="AI26" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ26" s="31" t="e">
+      <c r="AJ26" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK26" s="31" t="e">
+      <c r="AK26" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL26" s="31" t="e">
+      <c r="AL26" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM26" s="31" t="e">
+      <c r="AM26" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN26" s="31" t="e">
+      <c r="AN26" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO26" s="31" t="e">
+      <c r="AO26" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP26" s="31" t="e">
+      <c r="AP26" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ26" s="31" t="e">
+      <c r="AQ26" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR26" s="31" t="e">
+      <c r="AR26" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS26" s="31" t="e">
+      <c r="AS26" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT26" s="31" t="e">
+      <c r="AT26" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU26" s="31" t="e">
+      <c r="AU26" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV26" s="31" t="e">
+      <c r="AV26" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW26" s="31" t="e">
+      <c r="AW26" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX26" s="31" t="e">
+      <c r="AX26" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY26" s="31" t="e">
+      <c r="AY26" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ26" s="30" t="e">
+      <c r="AZ26" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA26" s="30" t="e">
+      <c r="BA26" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB26" s="30" t="e">
+      <c r="BB26" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC26" s="30" t="e">
+      <c r="BC26" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD26" s="31" t="e">
+      <c r="BD26" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE26" s="31" t="e">
+      <c r="BE26" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF26" s="31" t="e">
+      <c r="BF26" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG26" s="31" t="e">
+      <c r="BG26" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH26" s="31" t="e">
+      <c r="BH26" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI26" s="31" t="e">
+      <c r="BI26" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="27" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C27" s="3" t="s">
         <v>140</v>
       </c>
@@ -6945,175 +6929,175 @@
       <c r="K27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="22">
         <v>2</v>
       </c>
-      <c r="U27" s="31" t="e">
+      <c r="U27" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V27" s="31" t="e">
+      <c r="V27" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W27" s="31" t="e">
+      <c r="W27" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X27" s="31" t="e">
+      <c r="X27" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y27" s="31" t="e">
+      <c r="Y27" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z27" s="31" t="e">
+      <c r="Z27" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA27" s="31" t="e">
+      <c r="AA27" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB27" s="31" t="e">
+      <c r="AB27" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC27" s="31" t="e">
+      <c r="AC27" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD27" s="31" t="e">
+      <c r="AD27" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE27" s="31" t="e">
+      <c r="AE27" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF27" s="31" t="e">
+      <c r="AF27" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG27" s="31" t="e">
+      <c r="AG27" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH27" s="31" t="e">
+      <c r="AH27" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI27" s="31">
+      <c r="AI27" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ27" s="31" t="e">
+      <c r="AJ27" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK27" s="31" t="e">
+      <c r="AK27" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL27" s="31" t="e">
+      <c r="AL27" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM27" s="31" t="e">
+      <c r="AM27" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN27" s="31" t="e">
+      <c r="AN27" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO27" s="31" t="e">
+      <c r="AO27" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP27" s="31" t="e">
+      <c r="AP27" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ27" s="31" t="e">
+      <c r="AQ27" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR27" s="31" t="e">
+      <c r="AR27" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS27" s="31" t="e">
+      <c r="AS27" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT27" s="31" t="e">
+      <c r="AT27" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU27" s="31" t="e">
+      <c r="AU27" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV27" s="31" t="e">
+      <c r="AV27" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW27" s="31" t="e">
+      <c r="AW27" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX27" s="31" t="e">
+      <c r="AX27" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY27" s="31" t="e">
+      <c r="AY27" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ27" s="30" t="e">
+      <c r="AZ27" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA27" s="30" t="e">
+      <c r="BA27" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB27" s="30" t="e">
+      <c r="BB27" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC27" s="30" t="e">
+      <c r="BC27" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD27" s="31" t="e">
+      <c r="BD27" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE27" s="31" t="e">
+      <c r="BE27" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF27" s="31" t="e">
+      <c r="BF27" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG27" s="31" t="e">
+      <c r="BG27" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH27" s="31" t="e">
+      <c r="BH27" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI27" s="31" t="e">
+      <c r="BI27" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="28" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C28" s="3" t="s">
         <v>14</v>
       </c>
@@ -7140,175 +7124,175 @@
       <c r="K28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="22">
         <v>3</v>
       </c>
-      <c r="U28" s="31" t="e">
+      <c r="U28" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V28" s="31" t="e">
+      <c r="V28" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W28" s="31" t="e">
+      <c r="W28" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X28" s="31" t="e">
+      <c r="X28" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y28" s="31" t="e">
+      <c r="Y28" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z28" s="31" t="e">
+      <c r="Z28" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA28" s="31" t="e">
+      <c r="AA28" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB28" s="31" t="e">
+      <c r="AB28" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC28" s="31" t="e">
+      <c r="AC28" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD28" s="31" t="e">
+      <c r="AD28" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE28" s="31" t="e">
+      <c r="AE28" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF28" s="31" t="e">
+      <c r="AF28" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG28" s="31" t="e">
+      <c r="AG28" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH28" s="31" t="e">
+      <c r="AH28" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI28" s="31">
+      <c r="AI28" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ28" s="31" t="e">
+      <c r="AJ28" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK28" s="31" t="e">
+      <c r="AK28" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL28" s="31" t="e">
+      <c r="AL28" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM28" s="31" t="e">
+      <c r="AM28" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN28" s="31" t="e">
+      <c r="AN28" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO28" s="31" t="e">
+      <c r="AO28" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP28" s="31" t="e">
+      <c r="AP28" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ28" s="31" t="e">
+      <c r="AQ28" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR28" s="31" t="e">
+      <c r="AR28" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS28" s="31" t="e">
+      <c r="AS28" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT28" s="31" t="e">
+      <c r="AT28" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU28" s="31" t="e">
+      <c r="AU28" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV28" s="31" t="e">
+      <c r="AV28" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW28" s="31" t="e">
+      <c r="AW28" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX28" s="31" t="e">
+      <c r="AX28" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY28" s="31" t="e">
+      <c r="AY28" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ28" s="30" t="e">
+      <c r="AZ28" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA28" s="30" t="e">
+      <c r="BA28" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB28" s="30" t="e">
+      <c r="BB28" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC28" s="30" t="e">
+      <c r="BC28" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD28" s="31" t="e">
+      <c r="BD28" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE28" s="31" t="e">
+      <c r="BE28" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF28" s="31" t="e">
+      <c r="BF28" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG28" s="31" t="e">
+      <c r="BG28" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH28" s="31" t="e">
+      <c r="BH28" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI28" s="31" t="e">
+      <c r="BI28" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="29" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C29" s="3" t="s">
         <v>15</v>
       </c>
@@ -7335,175 +7319,175 @@
       <c r="K29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="T29" s="30">
+      <c r="T29" s="22">
         <v>4</v>
       </c>
-      <c r="U29" s="31" t="e">
+      <c r="U29" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V29" s="31" t="e">
+      <c r="V29" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W29" s="31" t="e">
+      <c r="W29" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X29" s="31" t="e">
+      <c r="X29" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y29" s="31" t="e">
+      <c r="Y29" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z29" s="31" t="e">
+      <c r="Z29" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA29" s="31" t="e">
+      <c r="AA29" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB29" s="31" t="e">
+      <c r="AB29" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC29" s="31" t="e">
+      <c r="AC29" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD29" s="31" t="e">
+      <c r="AD29" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE29" s="31" t="e">
+      <c r="AE29" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF29" s="31" t="e">
+      <c r="AF29" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG29" s="31" t="e">
+      <c r="AG29" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH29" s="31" t="e">
+      <c r="AH29" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI29" s="31">
+      <c r="AI29" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ29" s="31" t="e">
+      <c r="AJ29" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK29" s="31" t="e">
+      <c r="AK29" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL29" s="31" t="e">
+      <c r="AL29" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM29" s="31" t="e">
+      <c r="AM29" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN29" s="31" t="e">
+      <c r="AN29" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO29" s="31" t="e">
+      <c r="AO29" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP29" s="31" t="e">
+      <c r="AP29" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ29" s="31" t="e">
+      <c r="AQ29" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR29" s="31" t="e">
+      <c r="AR29" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS29" s="31" t="e">
+      <c r="AS29" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT29" s="31" t="e">
+      <c r="AT29" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU29" s="31" t="e">
+      <c r="AU29" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV29" s="31" t="e">
+      <c r="AV29" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW29" s="31" t="e">
+      <c r="AW29" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX29" s="31" t="e">
+      <c r="AX29" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY29" s="31" t="e">
+      <c r="AY29" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ29" s="30" t="e">
+      <c r="AZ29" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA29" s="30" t="e">
+      <c r="BA29" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB29" s="30" t="e">
+      <c r="BB29" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC29" s="30" t="e">
+      <c r="BC29" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD29" s="31" t="e">
+      <c r="BD29" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE29" s="31" t="e">
+      <c r="BE29" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF29" s="31" t="e">
+      <c r="BF29" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG29" s="31" t="e">
+      <c r="BG29" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH29" s="31" t="e">
+      <c r="BH29" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI29" s="31" t="e">
+      <c r="BI29" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="30" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C30" s="3" t="s">
         <v>16</v>
       </c>
@@ -7530,175 +7514,175 @@
       <c r="K30" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="T30" s="30">
+      <c r="T30" s="22">
         <v>5</v>
       </c>
-      <c r="U30" s="31" t="e">
+      <c r="U30" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V30" s="31" t="e">
+      <c r="V30" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W30" s="31" t="e">
+      <c r="W30" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X30" s="31" t="e">
+      <c r="X30" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y30" s="31" t="e">
+      <c r="Y30" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z30" s="31" t="e">
+      <c r="Z30" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA30" s="31" t="e">
+      <c r="AA30" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB30" s="31" t="e">
+      <c r="AB30" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC30" s="31" t="e">
+      <c r="AC30" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD30" s="31" t="e">
+      <c r="AD30" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE30" s="31" t="e">
+      <c r="AE30" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF30" s="31" t="e">
+      <c r="AF30" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG30" s="31" t="e">
+      <c r="AG30" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH30" s="31" t="e">
+      <c r="AH30" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI30" s="31">
+      <c r="AI30" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ30" s="31" t="e">
+      <c r="AJ30" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK30" s="31" t="e">
+      <c r="AK30" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL30" s="31" t="e">
+      <c r="AL30" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM30" s="31" t="e">
+      <c r="AM30" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN30" s="31" t="e">
+      <c r="AN30" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO30" s="31" t="e">
+      <c r="AO30" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP30" s="31" t="e">
+      <c r="AP30" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ30" s="31" t="e">
+      <c r="AQ30" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR30" s="31" t="e">
+      <c r="AR30" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS30" s="31" t="e">
+      <c r="AS30" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT30" s="31" t="e">
+      <c r="AT30" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU30" s="31" t="e">
+      <c r="AU30" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV30" s="31" t="e">
+      <c r="AV30" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW30" s="31" t="e">
+      <c r="AW30" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX30" s="31" t="e">
+      <c r="AX30" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY30" s="31" t="e">
+      <c r="AY30" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ30" s="30" t="e">
+      <c r="AZ30" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA30" s="30" t="e">
+      <c r="BA30" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB30" s="30" t="e">
+      <c r="BB30" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC30" s="30" t="e">
+      <c r="BC30" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD30" s="31" t="e">
+      <c r="BD30" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE30" s="31" t="e">
+      <c r="BE30" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF30" s="31" t="e">
+      <c r="BF30" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG30" s="31" t="e">
+      <c r="BG30" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH30" s="31" t="e">
+      <c r="BH30" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI30" s="31" t="e">
+      <c r="BI30" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="31" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C31" s="3" t="s">
         <v>17</v>
       </c>
@@ -7725,175 +7709,175 @@
       <c r="K31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="T31" s="30">
+      <c r="T31" s="22">
         <v>6</v>
       </c>
-      <c r="U31" s="31" t="e">
+      <c r="U31" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V31" s="31" t="e">
+      <c r="V31" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W31" s="31" t="e">
+      <c r="W31" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X31" s="31" t="e">
+      <c r="X31" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y31" s="31" t="e">
+      <c r="Y31" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z31" s="31" t="e">
+      <c r="Z31" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA31" s="31" t="e">
+      <c r="AA31" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB31" s="31" t="e">
+      <c r="AB31" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC31" s="31" t="e">
+      <c r="AC31" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD31" s="31" t="e">
+      <c r="AD31" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE31" s="31" t="e">
+      <c r="AE31" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF31" s="31" t="e">
+      <c r="AF31" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG31" s="31" t="e">
+      <c r="AG31" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH31" s="31" t="e">
+      <c r="AH31" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI31" s="31">
+      <c r="AI31" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ31" s="31" t="e">
+      <c r="AJ31" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK31" s="31" t="e">
+      <c r="AK31" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL31" s="31" t="e">
+      <c r="AL31" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM31" s="31" t="e">
+      <c r="AM31" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN31" s="31" t="e">
+      <c r="AN31" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO31" s="31" t="e">
+      <c r="AO31" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP31" s="31" t="e">
+      <c r="AP31" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ31" s="31" t="e">
+      <c r="AQ31" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR31" s="31" t="e">
+      <c r="AR31" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS31" s="31" t="e">
+      <c r="AS31" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT31" s="31" t="e">
+      <c r="AT31" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU31" s="31" t="e">
+      <c r="AU31" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV31" s="31" t="e">
+      <c r="AV31" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW31" s="31" t="e">
+      <c r="AW31" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX31" s="31" t="e">
+      <c r="AX31" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY31" s="31" t="e">
+      <c r="AY31" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ31" s="30" t="e">
+      <c r="AZ31" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA31" s="30" t="e">
+      <c r="BA31" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB31" s="30" t="e">
+      <c r="BB31" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC31" s="30" t="e">
+      <c r="BC31" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD31" s="31" t="e">
+      <c r="BD31" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE31" s="31" t="e">
+      <c r="BE31" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF31" s="31" t="e">
+      <c r="BF31" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG31" s="31" t="e">
+      <c r="BG31" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH31" s="31" t="e">
+      <c r="BH31" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI31" s="31" t="e">
+      <c r="BI31" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="32" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C32" s="3" t="s">
         <v>18</v>
       </c>
@@ -7920,175 +7904,175 @@
       <c r="K32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="T32" s="30">
+      <c r="T32" s="22">
         <v>7</v>
       </c>
-      <c r="U32" s="31" t="e">
+      <c r="U32" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V32" s="31" t="e">
+      <c r="V32" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W32" s="31" t="e">
+      <c r="W32" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X32" s="31" t="e">
+      <c r="X32" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y32" s="31" t="e">
+      <c r="Y32" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z32" s="31" t="e">
+      <c r="Z32" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA32" s="31" t="e">
+      <c r="AA32" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB32" s="31" t="e">
+      <c r="AB32" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC32" s="31" t="e">
+      <c r="AC32" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD32" s="31" t="e">
+      <c r="AD32" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE32" s="31" t="e">
+      <c r="AE32" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF32" s="31" t="e">
+      <c r="AF32" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG32" s="31" t="e">
+      <c r="AG32" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH32" s="31" t="e">
+      <c r="AH32" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI32" s="31">
+      <c r="AI32" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ32" s="31" t="e">
+      <c r="AJ32" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK32" s="31" t="e">
+      <c r="AK32" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL32" s="31" t="e">
+      <c r="AL32" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM32" s="31" t="e">
+      <c r="AM32" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN32" s="31" t="e">
+      <c r="AN32" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO32" s="31" t="e">
+      <c r="AO32" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP32" s="31" t="e">
+      <c r="AP32" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ32" s="31" t="e">
+      <c r="AQ32" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR32" s="31" t="e">
+      <c r="AR32" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS32" s="31" t="e">
+      <c r="AS32" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT32" s="31" t="e">
+      <c r="AT32" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU32" s="31" t="e">
+      <c r="AU32" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV32" s="31" t="e">
+      <c r="AV32" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW32" s="31" t="e">
+      <c r="AW32" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX32" s="31" t="e">
+      <c r="AX32" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY32" s="31" t="e">
+      <c r="AY32" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ32" s="30" t="e">
+      <c r="AZ32" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA32" s="30" t="e">
+      <c r="BA32" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB32" s="30" t="e">
+      <c r="BB32" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC32" s="30" t="e">
+      <c r="BC32" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD32" s="31" t="e">
+      <c r="BD32" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE32" s="31" t="e">
+      <c r="BE32" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF32" s="31" t="e">
+      <c r="BF32" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG32" s="31" t="e">
+      <c r="BG32" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH32" s="31" t="e">
+      <c r="BH32" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI32" s="31" t="e">
+      <c r="BI32" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="33" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C33" s="3" t="s">
         <v>157</v>
       </c>
@@ -8114,175 +8098,175 @@
       <c r="K33" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="T33" s="30">
+      <c r="T33" s="22">
         <v>8</v>
       </c>
-      <c r="U33" s="31" t="e">
+      <c r="U33" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V33" s="31" t="e">
+      <c r="V33" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W33" s="31" t="e">
+      <c r="W33" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X33" s="31" t="e">
+      <c r="X33" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y33" s="31" t="e">
+      <c r="Y33" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z33" s="31" t="e">
+      <c r="Z33" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA33" s="31" t="e">
+      <c r="AA33" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB33" s="31" t="e">
+      <c r="AB33" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC33" s="31" t="e">
+      <c r="AC33" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD33" s="31" t="e">
+      <c r="AD33" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE33" s="31" t="e">
+      <c r="AE33" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF33" s="31" t="e">
+      <c r="AF33" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG33" s="31" t="e">
+      <c r="AG33" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH33" s="31" t="e">
+      <c r="AH33" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI33" s="31">
+      <c r="AI33" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ33" s="31" t="e">
+      <c r="AJ33" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK33" s="31" t="e">
+      <c r="AK33" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL33" s="31" t="e">
+      <c r="AL33" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM33" s="31" t="e">
+      <c r="AM33" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN33" s="31" t="e">
+      <c r="AN33" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO33" s="31" t="e">
+      <c r="AO33" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP33" s="31" t="e">
+      <c r="AP33" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ33" s="31" t="e">
+      <c r="AQ33" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR33" s="31" t="e">
+      <c r="AR33" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS33" s="31" t="e">
+      <c r="AS33" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT33" s="31" t="e">
+      <c r="AT33" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU33" s="31" t="e">
+      <c r="AU33" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV33" s="31" t="e">
+      <c r="AV33" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW33" s="31" t="e">
+      <c r="AW33" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX33" s="31" t="e">
+      <c r="AX33" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY33" s="31" t="e">
+      <c r="AY33" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ33" s="30" t="e">
+      <c r="AZ33" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA33" s="30" t="e">
+      <c r="BA33" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB33" s="30" t="e">
+      <c r="BB33" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC33" s="30" t="e">
+      <c r="BC33" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD33" s="31" t="e">
+      <c r="BD33" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE33" s="31" t="e">
+      <c r="BE33" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF33" s="31" t="e">
+      <c r="BF33" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG33" s="31" t="e">
+      <c r="BG33" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH33" s="31" t="e">
+      <c r="BH33" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI33" s="31" t="e">
+      <c r="BI33" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="34" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
@@ -8309,175 +8293,175 @@
       <c r="K34" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="T34" s="30">
+      <c r="T34" s="22">
         <v>9</v>
       </c>
-      <c r="U34" s="31" t="e">
+      <c r="U34" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V34" s="31" t="e">
+      <c r="V34" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W34" s="31" t="e">
+      <c r="W34" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X34" s="31" t="e">
+      <c r="X34" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y34" s="31" t="e">
+      <c r="Y34" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z34" s="31" t="e">
+      <c r="Z34" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA34" s="31" t="e">
+      <c r="AA34" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB34" s="31" t="e">
+      <c r="AB34" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC34" s="31" t="e">
+      <c r="AC34" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD34" s="31" t="e">
+      <c r="AD34" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE34" s="31" t="e">
+      <c r="AE34" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF34" s="31" t="e">
+      <c r="AF34" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG34" s="31" t="e">
+      <c r="AG34" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH34" s="31" t="e">
+      <c r="AH34" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI34" s="31">
+      <c r="AI34" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ34" s="31" t="e">
+      <c r="AJ34" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK34" s="31" t="e">
+      <c r="AK34" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL34" s="31" t="e">
+      <c r="AL34" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM34" s="31" t="e">
+      <c r="AM34" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN34" s="31" t="e">
+      <c r="AN34" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO34" s="31" t="e">
+      <c r="AO34" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP34" s="31" t="e">
+      <c r="AP34" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ34" s="31" t="e">
+      <c r="AQ34" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR34" s="31" t="e">
+      <c r="AR34" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS34" s="31" t="e">
+      <c r="AS34" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT34" s="31" t="e">
+      <c r="AT34" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU34" s="31" t="e">
+      <c r="AU34" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV34" s="31" t="e">
+      <c r="AV34" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW34" s="31" t="e">
+      <c r="AW34" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX34" s="31" t="e">
+      <c r="AX34" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY34" s="31" t="e">
+      <c r="AY34" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ34" s="30" t="e">
+      <c r="AZ34" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA34" s="30" t="e">
+      <c r="BA34" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB34" s="30" t="e">
+      <c r="BB34" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC34" s="30" t="e">
+      <c r="BC34" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD34" s="31" t="e">
+      <c r="BD34" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE34" s="31" t="e">
+      <c r="BE34" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF34" s="31" t="e">
+      <c r="BF34" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG34" s="31" t="e">
+      <c r="BG34" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH34" s="31" t="e">
+      <c r="BH34" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI34" s="31" t="e">
+      <c r="BI34" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="35" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C35" s="3" t="s">
         <v>20</v>
       </c>
@@ -8504,175 +8488,175 @@
       <c r="K35" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="T35" s="30">
+      <c r="T35" s="22">
         <v>10</v>
       </c>
-      <c r="U35" s="31" t="e">
+      <c r="U35" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V35" s="31" t="e">
+      <c r="V35" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W35" s="31" t="e">
+      <c r="W35" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X35" s="31" t="e">
+      <c r="X35" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y35" s="31" t="e">
+      <c r="Y35" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z35" s="31" t="e">
+      <c r="Z35" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA35" s="31" t="e">
+      <c r="AA35" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB35" s="31" t="e">
+      <c r="AB35" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC35" s="31" t="e">
+      <c r="AC35" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD35" s="31" t="e">
+      <c r="AD35" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE35" s="31" t="e">
+      <c r="AE35" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF35" s="31" t="e">
+      <c r="AF35" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG35" s="31" t="e">
+      <c r="AG35" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH35" s="31" t="e">
+      <c r="AH35" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI35" s="31">
+      <c r="AI35" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ35" s="31" t="e">
+      <c r="AJ35" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK35" s="31" t="e">
+      <c r="AK35" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL35" s="31" t="e">
+      <c r="AL35" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM35" s="31" t="e">
+      <c r="AM35" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN35" s="31" t="e">
+      <c r="AN35" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO35" s="31" t="e">
+      <c r="AO35" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP35" s="31" t="e">
+      <c r="AP35" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ35" s="31" t="e">
+      <c r="AQ35" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR35" s="31" t="e">
+      <c r="AR35" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS35" s="31" t="e">
+      <c r="AS35" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT35" s="31" t="e">
+      <c r="AT35" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU35" s="31" t="e">
+      <c r="AU35" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV35" s="31" t="e">
+      <c r="AV35" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW35" s="31" t="e">
+      <c r="AW35" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX35" s="31" t="e">
+      <c r="AX35" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY35" s="31" t="e">
+      <c r="AY35" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ35" s="30" t="e">
+      <c r="AZ35" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA35" s="30" t="e">
+      <c r="BA35" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB35" s="30" t="e">
+      <c r="BB35" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC35" s="30" t="e">
+      <c r="BC35" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD35" s="31" t="e">
+      <c r="BD35" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE35" s="31" t="e">
+      <c r="BE35" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF35" s="31" t="e">
+      <c r="BF35" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG35" s="31" t="e">
+      <c r="BG35" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH35" s="31" t="e">
+      <c r="BH35" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI35" s="31" t="e">
+      <c r="BI35" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="36" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
@@ -8699,175 +8683,175 @@
       <c r="K36" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="T36" s="30">
+      <c r="T36" s="22">
         <v>11</v>
       </c>
-      <c r="U36" s="31" t="e">
+      <c r="U36" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V36" s="31" t="e">
+      <c r="V36" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W36" s="31" t="e">
+      <c r="W36" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X36" s="31" t="e">
+      <c r="X36" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y36" s="31" t="e">
+      <c r="Y36" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z36" s="31" t="e">
+      <c r="Z36" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA36" s="31" t="e">
+      <c r="AA36" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB36" s="31" t="e">
+      <c r="AB36" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC36" s="31" t="e">
+      <c r="AC36" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD36" s="31" t="e">
+      <c r="AD36" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE36" s="31" t="e">
+      <c r="AE36" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF36" s="31" t="e">
+      <c r="AF36" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG36" s="31" t="e">
+      <c r="AG36" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH36" s="31" t="e">
+      <c r="AH36" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI36" s="31">
+      <c r="AI36" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="31" t="e">
+      <c r="AJ36" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK36" s="31" t="e">
+      <c r="AK36" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL36" s="31" t="e">
+      <c r="AL36" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM36" s="31" t="e">
+      <c r="AM36" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN36" s="31" t="e">
+      <c r="AN36" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO36" s="31" t="e">
+      <c r="AO36" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP36" s="31" t="e">
+      <c r="AP36" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ36" s="31" t="e">
+      <c r="AQ36" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR36" s="31" t="e">
+      <c r="AR36" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS36" s="31" t="e">
+      <c r="AS36" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT36" s="31" t="e">
+      <c r="AT36" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU36" s="31" t="e">
+      <c r="AU36" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV36" s="31" t="e">
+      <c r="AV36" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW36" s="31" t="e">
+      <c r="AW36" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX36" s="31" t="e">
+      <c r="AX36" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY36" s="31" t="e">
+      <c r="AY36" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ36" s="30" t="e">
+      <c r="AZ36" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA36" s="30" t="e">
+      <c r="BA36" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB36" s="30" t="e">
+      <c r="BB36" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC36" s="30" t="e">
+      <c r="BC36" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD36" s="31" t="e">
+      <c r="BD36" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE36" s="31" t="e">
+      <c r="BE36" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF36" s="31" t="e">
+      <c r="BF36" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG36" s="31" t="e">
+      <c r="BG36" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH36" s="31" t="e">
+      <c r="BH36" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI36" s="31" t="e">
+      <c r="BI36" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="37" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H37" s="4" t="s">
         <v>167</v>
       </c>
@@ -8881,181 +8865,181 @@
       <c r="K37" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="T37" s="30">
+      <c r="T37" s="22">
         <v>12</v>
       </c>
-      <c r="U37" s="31" t="e">
+      <c r="U37" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V37" s="31" t="e">
+      <c r="V37" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W37" s="31" t="e">
+      <c r="W37" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X37" s="31" t="e">
+      <c r="X37" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y37" s="31" t="e">
+      <c r="Y37" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z37" s="31" t="e">
+      <c r="Z37" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA37" s="31" t="e">
+      <c r="AA37" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB37" s="31" t="e">
+      <c r="AB37" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC37" s="31" t="e">
+      <c r="AC37" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD37" s="31" t="e">
+      <c r="AD37" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE37" s="31" t="e">
+      <c r="AE37" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF37" s="31" t="e">
+      <c r="AF37" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG37" s="31" t="e">
+      <c r="AG37" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH37" s="31" t="e">
+      <c r="AH37" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI37" s="31">
+      <c r="AI37" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ37" s="31" t="e">
+      <c r="AJ37" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK37" s="31" t="e">
+      <c r="AK37" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL37" s="31" t="e">
+      <c r="AL37" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM37" s="31" t="e">
+      <c r="AM37" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN37" s="31" t="e">
+      <c r="AN37" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO37" s="31" t="e">
+      <c r="AO37" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP37" s="31" t="e">
+      <c r="AP37" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ37" s="31" t="e">
+      <c r="AQ37" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR37" s="31" t="e">
+      <c r="AR37" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS37" s="31" t="e">
+      <c r="AS37" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT37" s="31" t="e">
+      <c r="AT37" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU37" s="31" t="e">
+      <c r="AU37" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV37" s="31" t="e">
+      <c r="AV37" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW37" s="31" t="e">
+      <c r="AW37" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX37" s="31" t="e">
+      <c r="AX37" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY37" s="31" t="e">
+      <c r="AY37" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ37" s="30" t="e">
+      <c r="AZ37" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA37" s="30" t="e">
+      <c r="BA37" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB37" s="30" t="e">
+      <c r="BB37" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC37" s="30" t="e">
+      <c r="BC37" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD37" s="31" t="e">
+      <c r="BD37" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE37" s="31" t="e">
+      <c r="BE37" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF37" s="31" t="e">
+      <c r="BF37" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG37" s="31" t="e">
+      <c r="BG37" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH37" s="31" t="e">
+      <c r="BH37" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI37" s="31" t="e">
+      <c r="BI37" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="38" spans="3:61" x14ac:dyDescent="0.25">
-      <c r="C38" s="23" t="s">
+    <row r="38" spans="3:61" x14ac:dyDescent="0.3">
+      <c r="C38" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
       <c r="H38" s="4" t="s">
         <v>27</v>
       </c>
@@ -9069,175 +9053,175 @@
       <c r="K38" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="T38" s="30">
+      <c r="T38" s="22">
         <v>13</v>
       </c>
-      <c r="U38" s="31" t="e">
+      <c r="U38" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V38" s="31" t="e">
+      <c r="V38" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W38" s="31" t="e">
+      <c r="W38" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X38" s="31" t="e">
+      <c r="X38" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y38" s="31" t="e">
+      <c r="Y38" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z38" s="31" t="e">
+      <c r="Z38" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA38" s="31" t="e">
+      <c r="AA38" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB38" s="31" t="e">
+      <c r="AB38" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC38" s="31" t="e">
+      <c r="AC38" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD38" s="31" t="e">
+      <c r="AD38" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE38" s="31" t="e">
+      <c r="AE38" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF38" s="31" t="e">
+      <c r="AF38" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG38" s="31" t="e">
+      <c r="AG38" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH38" s="31" t="e">
+      <c r="AH38" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI38" s="31">
+      <c r="AI38" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ38" s="31" t="e">
+      <c r="AJ38" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK38" s="31" t="e">
+      <c r="AK38" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL38" s="31" t="e">
+      <c r="AL38" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM38" s="31" t="e">
+      <c r="AM38" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN38" s="31" t="e">
+      <c r="AN38" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO38" s="31" t="e">
+      <c r="AO38" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP38" s="31" t="e">
+      <c r="AP38" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ38" s="31" t="e">
+      <c r="AQ38" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR38" s="31" t="e">
+      <c r="AR38" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS38" s="31" t="e">
+      <c r="AS38" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT38" s="31" t="e">
+      <c r="AT38" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU38" s="31" t="e">
+      <c r="AU38" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV38" s="31" t="e">
+      <c r="AV38" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW38" s="31" t="e">
+      <c r="AW38" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX38" s="31" t="e">
+      <c r="AX38" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY38" s="31" t="e">
+      <c r="AY38" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ38" s="30" t="e">
+      <c r="AZ38" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA38" s="30" t="e">
+      <c r="BA38" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB38" s="30" t="e">
+      <c r="BB38" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC38" s="30" t="e">
+      <c r="BC38" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD38" s="31" t="e">
+      <c r="BD38" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE38" s="31" t="e">
+      <c r="BE38" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF38" s="31" t="e">
+      <c r="BF38" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG38" s="31" t="e">
+      <c r="BG38" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH38" s="31" t="e">
+      <c r="BH38" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI38" s="31" t="e">
+      <c r="BI38" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="39" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C39" s="2" t="s">
         <v>105</v>
       </c>
@@ -9263,175 +9247,175 @@
       <c r="K39" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="T39" s="30">
+      <c r="T39" s="22">
         <v>14</v>
       </c>
-      <c r="U39" s="31" t="e">
+      <c r="U39" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V39" s="31" t="e">
+      <c r="V39" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W39" s="31" t="e">
+      <c r="W39" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X39" s="31" t="e">
+      <c r="X39" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y39" s="31" t="e">
+      <c r="Y39" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z39" s="31" t="e">
+      <c r="Z39" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA39" s="31" t="e">
+      <c r="AA39" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB39" s="31" t="e">
+      <c r="AB39" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC39" s="31" t="e">
+      <c r="AC39" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD39" s="31" t="e">
+      <c r="AD39" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE39" s="31" t="e">
+      <c r="AE39" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF39" s="31" t="e">
+      <c r="AF39" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG39" s="31" t="e">
+      <c r="AG39" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH39" s="31" t="e">
+      <c r="AH39" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI39" s="31">
+      <c r="AI39" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ39" s="31" t="e">
+      <c r="AJ39" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK39" s="31" t="e">
+      <c r="AK39" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL39" s="31" t="e">
+      <c r="AL39" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM39" s="31" t="e">
+      <c r="AM39" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN39" s="31" t="e">
+      <c r="AN39" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO39" s="31" t="e">
+      <c r="AO39" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP39" s="31" t="e">
+      <c r="AP39" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ39" s="31" t="e">
+      <c r="AQ39" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR39" s="31" t="e">
+      <c r="AR39" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS39" s="31" t="e">
+      <c r="AS39" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT39" s="31" t="e">
+      <c r="AT39" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU39" s="31" t="e">
+      <c r="AU39" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV39" s="31" t="e">
+      <c r="AV39" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW39" s="31" t="e">
+      <c r="AW39" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX39" s="31" t="e">
+      <c r="AX39" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY39" s="31" t="e">
+      <c r="AY39" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ39" s="30" t="e">
+      <c r="AZ39" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA39" s="30" t="e">
+      <c r="BA39" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB39" s="30" t="e">
+      <c r="BB39" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC39" s="30" t="e">
+      <c r="BC39" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD39" s="31" t="e">
+      <c r="BD39" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE39" s="31" t="e">
+      <c r="BE39" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF39" s="31" t="e">
+      <c r="BF39" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG39" s="31" t="e">
+      <c r="BG39" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH39" s="31" t="e">
+      <c r="BH39" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI39" s="31" t="e">
+      <c r="BI39" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="40" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C40" s="6" t="s">
         <v>173</v>
       </c>
@@ -9458,175 +9442,175 @@
       <c r="K40" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="T40" s="30">
+      <c r="T40" s="22">
         <v>15</v>
       </c>
-      <c r="U40" s="31" t="e">
+      <c r="U40" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V40" s="31" t="e">
+      <c r="V40" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W40" s="31" t="e">
+      <c r="W40" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X40" s="31" t="e">
+      <c r="X40" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y40" s="31" t="e">
+      <c r="Y40" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z40" s="31" t="e">
+      <c r="Z40" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA40" s="31" t="e">
+      <c r="AA40" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB40" s="31" t="e">
+      <c r="AB40" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC40" s="31" t="e">
+      <c r="AC40" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD40" s="31" t="e">
+      <c r="AD40" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE40" s="31" t="e">
+      <c r="AE40" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF40" s="31" t="e">
+      <c r="AF40" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG40" s="31" t="e">
+      <c r="AG40" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH40" s="31" t="e">
+      <c r="AH40" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI40" s="31">
+      <c r="AI40" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="31" t="e">
+      <c r="AJ40" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK40" s="31" t="e">
+      <c r="AK40" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL40" s="31" t="e">
+      <c r="AL40" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM40" s="31" t="e">
+      <c r="AM40" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN40" s="31" t="e">
+      <c r="AN40" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO40" s="31" t="e">
+      <c r="AO40" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP40" s="31" t="e">
+      <c r="AP40" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ40" s="31" t="e">
+      <c r="AQ40" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR40" s="31" t="e">
+      <c r="AR40" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS40" s="31" t="e">
+      <c r="AS40" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT40" s="31" t="e">
+      <c r="AT40" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU40" s="31" t="e">
+      <c r="AU40" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV40" s="31" t="e">
+      <c r="AV40" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW40" s="31" t="e">
+      <c r="AW40" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX40" s="31" t="e">
+      <c r="AX40" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY40" s="31" t="e">
+      <c r="AY40" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ40" s="30" t="e">
+      <c r="AZ40" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA40" s="30" t="e">
+      <c r="BA40" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB40" s="30" t="e">
+      <c r="BB40" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC40" s="30" t="e">
+      <c r="BC40" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD40" s="31" t="e">
+      <c r="BD40" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE40" s="31" t="e">
+      <c r="BE40" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF40" s="31" t="e">
+      <c r="BF40" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG40" s="31" t="e">
+      <c r="BG40" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH40" s="31" t="e">
+      <c r="BH40" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI40" s="31" t="e">
+      <c r="BI40" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="41" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C41" s="6" t="s">
         <v>22</v>
       </c>
@@ -9653,175 +9637,175 @@
       <c r="K41" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="T41" s="30">
+      <c r="T41" s="22">
         <v>16</v>
       </c>
-      <c r="U41" s="31" t="e">
+      <c r="U41" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V41" s="31" t="e">
+      <c r="V41" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W41" s="31" t="e">
+      <c r="W41" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X41" s="31" t="e">
+      <c r="X41" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y41" s="31" t="e">
+      <c r="Y41" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z41" s="31" t="e">
+      <c r="Z41" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA41" s="31" t="e">
+      <c r="AA41" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB41" s="31" t="e">
+      <c r="AB41" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC41" s="31" t="e">
+      <c r="AC41" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD41" s="31" t="e">
+      <c r="AD41" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE41" s="31" t="e">
+      <c r="AE41" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF41" s="31" t="e">
+      <c r="AF41" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG41" s="31" t="e">
+      <c r="AG41" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH41" s="31" t="e">
+      <c r="AH41" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI41" s="31">
+      <c r="AI41" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ41" s="31" t="e">
+      <c r="AJ41" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK41" s="31" t="e">
+      <c r="AK41" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL41" s="31" t="e">
+      <c r="AL41" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM41" s="31" t="e">
+      <c r="AM41" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN41" s="31" t="e">
+      <c r="AN41" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO41" s="31" t="e">
+      <c r="AO41" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP41" s="31" t="e">
+      <c r="AP41" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ41" s="31" t="e">
+      <c r="AQ41" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR41" s="31" t="e">
+      <c r="AR41" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS41" s="31" t="e">
+      <c r="AS41" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT41" s="31" t="e">
+      <c r="AT41" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU41" s="31" t="e">
+      <c r="AU41" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV41" s="31" t="e">
+      <c r="AV41" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW41" s="31" t="e">
+      <c r="AW41" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX41" s="31" t="e">
+      <c r="AX41" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY41" s="31" t="e">
+      <c r="AY41" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ41" s="30" t="e">
+      <c r="AZ41" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA41" s="30" t="e">
+      <c r="BA41" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB41" s="30" t="e">
+      <c r="BB41" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC41" s="30" t="e">
+      <c r="BC41" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD41" s="31" t="e">
+      <c r="BD41" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE41" s="31" t="e">
+      <c r="BE41" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF41" s="31" t="e">
+      <c r="BF41" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG41" s="31" t="e">
+      <c r="BG41" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH41" s="31" t="e">
+      <c r="BH41" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI41" s="31" t="e">
+      <c r="BI41" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="42" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C42" s="6" t="s">
         <v>180</v>
       </c>
@@ -9848,175 +9832,175 @@
       <c r="K42" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="T42" s="30">
+      <c r="T42" s="22">
         <v>17</v>
       </c>
-      <c r="U42" s="31" t="e">
+      <c r="U42" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V42" s="31" t="e">
+      <c r="V42" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W42" s="31" t="e">
+      <c r="W42" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X42" s="31" t="e">
+      <c r="X42" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y42" s="31" t="e">
+      <c r="Y42" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z42" s="31" t="e">
+      <c r="Z42" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA42" s="31" t="e">
+      <c r="AA42" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB42" s="31" t="e">
+      <c r="AB42" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC42" s="31" t="e">
+      <c r="AC42" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD42" s="31" t="e">
+      <c r="AD42" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE42" s="31" t="e">
+      <c r="AE42" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF42" s="31" t="e">
+      <c r="AF42" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG42" s="31" t="e">
+      <c r="AG42" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH42" s="31" t="e">
+      <c r="AH42" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI42" s="31">
+      <c r="AI42" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ42" s="31" t="e">
+      <c r="AJ42" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK42" s="31" t="e">
+      <c r="AK42" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL42" s="31" t="e">
+      <c r="AL42" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM42" s="31" t="e">
+      <c r="AM42" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN42" s="31" t="e">
+      <c r="AN42" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO42" s="31" t="e">
+      <c r="AO42" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP42" s="31" t="e">
+      <c r="AP42" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ42" s="31" t="e">
+      <c r="AQ42" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR42" s="31" t="e">
+      <c r="AR42" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS42" s="31" t="e">
+      <c r="AS42" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT42" s="31" t="e">
+      <c r="AT42" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU42" s="31" t="e">
+      <c r="AU42" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV42" s="31" t="e">
+      <c r="AV42" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW42" s="31" t="e">
+      <c r="AW42" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX42" s="31" t="e">
+      <c r="AX42" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY42" s="31" t="e">
+      <c r="AY42" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ42" s="30" t="e">
+      <c r="AZ42" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA42" s="30" t="e">
+      <c r="BA42" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB42" s="30" t="e">
+      <c r="BB42" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC42" s="30" t="e">
+      <c r="BC42" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD42" s="31" t="e">
+      <c r="BD42" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE42" s="31" t="e">
+      <c r="BE42" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF42" s="31" t="e">
+      <c r="BF42" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG42" s="31" t="e">
+      <c r="BG42" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH42" s="31" t="e">
+      <c r="BH42" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI42" s="31" t="e">
+      <c r="BI42" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="43" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C43" s="6" t="s">
         <v>185</v>
       </c>
@@ -10043,175 +10027,175 @@
       <c r="K43" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="T43" s="30">
+      <c r="T43" s="22">
         <v>18</v>
       </c>
-      <c r="U43" s="31" t="e">
+      <c r="U43" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V43" s="31" t="e">
+      <c r="V43" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W43" s="31" t="e">
+      <c r="W43" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X43" s="31" t="e">
+      <c r="X43" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y43" s="31" t="e">
+      <c r="Y43" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z43" s="31" t="e">
+      <c r="Z43" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA43" s="31" t="e">
+      <c r="AA43" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB43" s="31" t="e">
+      <c r="AB43" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC43" s="31" t="e">
+      <c r="AC43" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD43" s="31" t="e">
+      <c r="AD43" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE43" s="31" t="e">
+      <c r="AE43" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF43" s="31" t="e">
+      <c r="AF43" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG43" s="31" t="e">
+      <c r="AG43" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH43" s="31" t="e">
+      <c r="AH43" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI43" s="31">
+      <c r="AI43" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ43" s="31" t="e">
+      <c r="AJ43" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK43" s="31" t="e">
+      <c r="AK43" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL43" s="31" t="e">
+      <c r="AL43" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM43" s="31" t="e">
+      <c r="AM43" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN43" s="31" t="e">
+      <c r="AN43" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO43" s="31" t="e">
+      <c r="AO43" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP43" s="31" t="e">
+      <c r="AP43" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ43" s="31" t="e">
+      <c r="AQ43" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR43" s="31" t="e">
+      <c r="AR43" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS43" s="31" t="e">
+      <c r="AS43" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT43" s="31" t="e">
+      <c r="AT43" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU43" s="31" t="e">
+      <c r="AU43" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV43" s="31" t="e">
+      <c r="AV43" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW43" s="31" t="e">
+      <c r="AW43" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX43" s="31" t="e">
+      <c r="AX43" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY43" s="31" t="e">
+      <c r="AY43" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ43" s="30" t="e">
+      <c r="AZ43" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA43" s="30" t="e">
+      <c r="BA43" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB43" s="30" t="e">
+      <c r="BB43" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC43" s="30" t="e">
+      <c r="BC43" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD43" s="31" t="e">
+      <c r="BD43" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE43" s="31" t="e">
+      <c r="BE43" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF43" s="31" t="e">
+      <c r="BF43" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG43" s="31" t="e">
+      <c r="BG43" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH43" s="31" t="e">
+      <c r="BH43" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI43" s="31" t="e">
+      <c r="BI43" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="44" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:61" x14ac:dyDescent="0.3">
       <c r="C44" s="6" t="s">
         <v>189</v>
       </c>
@@ -10238,175 +10222,175 @@
       <c r="K44" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="T44" s="30">
+      <c r="T44" s="22">
         <v>19</v>
       </c>
-      <c r="U44" s="31" t="e">
+      <c r="U44" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V44" s="31" t="e">
+      <c r="V44" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W44" s="31" t="e">
+      <c r="W44" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X44" s="31" t="e">
+      <c r="X44" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y44" s="31" t="e">
+      <c r="Y44" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z44" s="31" t="e">
+      <c r="Z44" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA44" s="31" t="e">
+      <c r="AA44" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB44" s="31" t="e">
+      <c r="AB44" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC44" s="31" t="e">
+      <c r="AC44" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD44" s="31" t="e">
+      <c r="AD44" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE44" s="31" t="e">
+      <c r="AE44" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF44" s="31" t="e">
+      <c r="AF44" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG44" s="31" t="e">
+      <c r="AG44" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH44" s="31" t="e">
+      <c r="AH44" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI44" s="31">
+      <c r="AI44" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ44" s="31" t="e">
+      <c r="AJ44" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK44" s="31" t="e">
+      <c r="AK44" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL44" s="31" t="e">
+      <c r="AL44" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM44" s="31" t="e">
+      <c r="AM44" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN44" s="31" t="e">
+      <c r="AN44" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO44" s="31" t="e">
+      <c r="AO44" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP44" s="31" t="e">
+      <c r="AP44" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ44" s="31" t="e">
+      <c r="AQ44" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR44" s="31" t="e">
+      <c r="AR44" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS44" s="31" t="e">
+      <c r="AS44" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT44" s="31" t="e">
+      <c r="AT44" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU44" s="31" t="e">
+      <c r="AU44" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV44" s="31" t="e">
+      <c r="AV44" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW44" s="31" t="e">
+      <c r="AW44" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX44" s="31" t="e">
+      <c r="AX44" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY44" s="31" t="e">
+      <c r="AY44" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ44" s="30" t="e">
+      <c r="AZ44" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA44" s="30" t="e">
+      <c r="BA44" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB44" s="30" t="e">
+      <c r="BB44" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC44" s="30" t="e">
+      <c r="BC44" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD44" s="31" t="e">
+      <c r="BD44" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE44" s="31" t="e">
+      <c r="BE44" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF44" s="31" t="e">
+      <c r="BF44" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG44" s="31" t="e">
+      <c r="BG44" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH44" s="31" t="e">
+      <c r="BH44" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI44" s="31" t="e">
+      <c r="BI44" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="45" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H45" s="3" t="s">
         <v>193</v>
       </c>
@@ -10420,175 +10404,175 @@
       <c r="K45" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="T45" s="30">
+      <c r="T45" s="22">
         <v>20</v>
       </c>
-      <c r="U45" s="31" t="e">
+      <c r="U45" s="23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="V45" s="31" t="e">
+      <c r="V45" s="23" t="e">
         <f t="shared" si="1"/>
         <v>#NUM!</v>
       </c>
-      <c r="W45" s="31" t="e">
+      <c r="W45" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#NUM!</v>
       </c>
-      <c r="X45" s="31" t="e">
+      <c r="X45" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="Y45" s="31" t="e">
+      <c r="Y45" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="Z45" s="31" t="e">
+      <c r="Z45" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="AA45" s="31" t="e">
+      <c r="AA45" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="AB45" s="31" t="e">
+      <c r="AB45" s="23" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="AC45" s="31" t="e">
+      <c r="AC45" s="23" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="AD45" s="31" t="e">
+      <c r="AD45" s="23" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
-      <c r="AE45" s="31" t="e">
+      <c r="AE45" s="23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF45" s="31" t="e">
+      <c r="AF45" s="23" t="e">
         <f t="shared" si="11"/>
         <v>#NUM!</v>
       </c>
-      <c r="AG45" s="31" t="e">
+      <c r="AG45" s="23" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
-      <c r="AH45" s="31" t="e">
+      <c r="AH45" s="23" t="e">
         <f t="shared" si="13"/>
         <v>#NUM!</v>
       </c>
-      <c r="AI45" s="31">
+      <c r="AI45" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AJ45" s="31" t="e">
+      <c r="AJ45" s="23" t="e">
         <f t="shared" si="15"/>
         <v>#NUM!</v>
       </c>
-      <c r="AK45" s="31" t="e">
+      <c r="AK45" s="23" t="e">
         <f t="shared" si="16"/>
         <v>#NUM!</v>
       </c>
-      <c r="AL45" s="31" t="e">
+      <c r="AL45" s="23" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM45" s="31" t="e">
+      <c r="AM45" s="23" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AN45" s="31" t="e">
+      <c r="AN45" s="23" t="e">
         <f t="shared" si="19"/>
         <v>#NUM!</v>
       </c>
-      <c r="AO45" s="31" t="e">
+      <c r="AO45" s="23" t="e">
         <f t="shared" si="20"/>
         <v>#NUM!</v>
       </c>
-      <c r="AP45" s="31" t="e">
+      <c r="AP45" s="23" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ45" s="31" t="e">
+      <c r="AQ45" s="23" t="e">
         <f t="shared" si="22"/>
         <v>#NUM!</v>
       </c>
-      <c r="AR45" s="31" t="e">
+      <c r="AR45" s="23" t="e">
         <f t="shared" si="23"/>
         <v>#NUM!</v>
       </c>
-      <c r="AS45" s="31" t="e">
+      <c r="AS45" s="23" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT45" s="31" t="e">
+      <c r="AT45" s="23" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU45" s="31" t="e">
+      <c r="AU45" s="23" t="e">
         <f t="shared" si="26"/>
         <v>#NUM!</v>
       </c>
-      <c r="AV45" s="31" t="e">
+      <c r="AV45" s="23" t="e">
         <f t="shared" si="27"/>
         <v>#NUM!</v>
       </c>
-      <c r="AW45" s="31" t="e">
+      <c r="AW45" s="23" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AX45" s="31" t="e">
+      <c r="AX45" s="23" t="e">
         <f t="shared" si="29"/>
         <v>#NUM!</v>
       </c>
-      <c r="AY45" s="31" t="e">
+      <c r="AY45" s="23" t="e">
         <f t="shared" si="30"/>
         <v>#NUM!</v>
       </c>
-      <c r="AZ45" s="30" t="e">
+      <c r="AZ45" s="22" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA45" s="30" t="e">
+      <c r="BA45" s="22" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BB45" s="30" t="e">
+      <c r="BB45" s="22" t="e">
         <f t="shared" si="33"/>
         <v>#NUM!</v>
       </c>
-      <c r="BC45" s="30" t="e">
+      <c r="BC45" s="22" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BD45" s="31" t="e">
+      <c r="BD45" s="23" t="e">
         <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BE45" s="31" t="e">
+      <c r="BE45" s="23" t="e">
         <f t="shared" si="36"/>
         <v>#N/A</v>
       </c>
-      <c r="BF45" s="31" t="e">
+      <c r="BF45" s="23" t="e">
         <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
-      <c r="BG45" s="31" t="e">
+      <c r="BG45" s="23" t="e">
         <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
-      <c r="BH45" s="31" t="e">
+      <c r="BH45" s="23" t="e">
         <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
-      <c r="BI45" s="31" t="e">
+      <c r="BI45" s="23" t="e">
         <f t="shared" si="40"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="46" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H46" s="3" t="s">
         <v>35</v>
       </c>
@@ -10603,7 +10587,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="47" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
@@ -10618,7 +10602,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="3:61" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:61" x14ac:dyDescent="0.3">
       <c r="H48" s="3" t="s">
         <v>37</v>
       </c>
@@ -10633,7 +10617,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H49" s="3" t="s">
         <v>38</v>
       </c>
@@ -10648,7 +10632,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H50" s="4" t="s">
         <v>39</v>
       </c>
@@ -10663,7 +10647,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H51" s="4" t="s">
         <v>40</v>
       </c>
@@ -10678,7 +10662,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H52" s="4" t="s">
         <v>41</v>
       </c>
@@ -10693,7 +10677,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H53" s="4" t="s">
         <v>42</v>
       </c>
@@ -10708,7 +10692,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H54" s="4" t="s">
         <v>43</v>
       </c>
@@ -10723,7 +10707,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H55" s="4" t="s">
         <v>44</v>
       </c>
@@ -10738,15 +10722,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H57" s="19" t="s">
+    <row r="57" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H57" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="21"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="29"/>
     </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H58" s="2" t="s">
         <v>105</v>
       </c>
@@ -10760,7 +10744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H59" s="18" t="s">
         <v>45</v>
       </c>
@@ -10775,7 +10759,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H60" s="18" t="s">
         <v>46</v>
       </c>
@@ -10790,7 +10774,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H61" s="18" t="s">
         <v>47</v>
       </c>
@@ -10805,7 +10789,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H62" s="17" t="s">
         <v>48</v>
       </c>
@@ -10820,7 +10804,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H63" s="17" t="s">
         <v>49</v>
       </c>
@@ -10835,7 +10819,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H64" s="17" t="s">
         <v>50</v>
       </c>
@@ -10850,7 +10834,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H65" s="17" t="s">
         <v>51</v>
       </c>
@@ -10865,7 +10849,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H66" s="17" t="s">
         <v>52</v>
       </c>
@@ -10880,7 +10864,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H67" s="17" t="s">
         <v>215</v>
       </c>
@@ -10918,32 +10902,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94AC071-6EFB-40EC-A8D8-2A8F2EEE54FA}">
   <dimension ref="C15:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="3:5" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C15" s="34" t="s">
+    <row r="15" spans="3:5" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="C15" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="24" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="3:5" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C16" s="35">
+    <row r="16" spans="3:5" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="C16" s="25">
         <v>320</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="26">
         <f>C16/25.4</f>
         <v>12.598425196850394</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="26">
         <f>D16/12</f>
         <v>1.0498687664041995</v>
       </c>
@@ -10956,7 +10940,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1BD15F-24D0-4D73-A089-9C6E4F7E1683}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
